--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Western Sydney Wanderers</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S2" t="n">
         <v>3.05</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -942,31 +942,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.4</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.47</v>
+        <v>2.62</v>
       </c>
       <c r="I3" t="n">
-        <v>1.59</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.66</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>1.47</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>1.59</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,201 +1308,395 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:41:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Lanus</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>2.02</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>2.2</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>4.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>5.1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>3.3</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.74</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-11 04:33:47</t>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>2.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -799,7 +799,7 @@
         <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
         <v>2.3</v>
@@ -841,7 +841,7 @@
         <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
@@ -898,19 +898,19 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD2" t="n">
         <v>8</v>
       </c>
-      <c r="BC2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
         <v>21</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dalian Yingbo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S3" t="n">
         <v>3.05</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.4</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.47</v>
+        <v>2.62</v>
       </c>
       <c r="I4" t="n">
-        <v>1.59</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1330,31 +1330,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>1.59</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,201 +1502,395 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-11 08:49:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Lanus</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>4.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>5.1</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>3.3</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.48</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>2.74</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-11 06:41:37</t>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,16 +790,16 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
         <v>2.3</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -874,7 +874,7 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
@@ -898,16 +898,16 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
         <v>8.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1014,13 +1014,13 @@
         <v>20</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
         <v>16</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>13</v>
@@ -1032,13 +1032,13 @@
         <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
         <v>60</v>
@@ -1068,7 +1068,7 @@
         <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1092,19 +1092,19 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
         <v>20</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Chiangrai Utd</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA4" t="n">
         <v>3.95</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -1330,31 +1330,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.2</v>
+        <v>2.58</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>1.59</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,201 +1696,395 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 08:49:48</t>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Lanus</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="F8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H8" t="n">
         <v>4.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>5.1</v>
       </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="J8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.3</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.74</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-03-11 08:49:48</t>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-11 10:57:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
         <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
         <v>3.05</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
         <v>1.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
         <v>19.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H4" t="n">
         <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1193,7 +1193,7 @@
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W4" t="n">
         <v>1.36</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Paradou</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>980</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>8.800000000000001</v>
+        <v>980</v>
       </c>
       <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>980</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K6" t="n">
+        <v>980</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.48</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.51</v>
-      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,378 +1713,1736 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
         <v>2.16</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 10:57:30</t>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UTA Arad</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hermannstadt</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Slavia Sofia</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Arges Pitesti</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Al-Quadisiya (KSA)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Al Riyadh SC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Lanus</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F15" t="n">
         <v>2.02</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="G15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H15" t="n">
         <v>4.5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I15" t="n">
         <v>5.1</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J15" t="n">
         <v>3.1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K15" t="n">
         <v>3.3</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.74</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-03-11 10:57:30</t>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:05:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
         <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>3.05</v>
@@ -862,7 +862,7 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP2" t="n">
         <v>6.4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
         <v>2.26</v>
@@ -993,7 +993,7 @@
         <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
         <v>2.28</v>
@@ -1011,10 +1011,10 @@
         <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
         <v>16</v>
@@ -1026,7 +1026,7 @@
         <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
         <v>26</v>
@@ -1038,7 +1038,7 @@
         <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>60</v>
@@ -1056,7 +1056,7 @@
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP3" t="n">
         <v>13.5</v>
@@ -1083,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
@@ -1098,7 +1098,7 @@
         <v>6</v>
       </c>
       <c r="BC3" t="n">
-        <v>30</v>
+        <v>5.7</v>
       </c>
       <c r="BD3" t="n">
         <v>34</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
         <v>980</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -1748,13 +1748,13 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.71</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
         <v>1.71</v>
@@ -1763,25 +1763,25 @@
         <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
         <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="Y7" t="n">
         <v>980</v>
@@ -1802,7 +1802,7 @@
         <v>980</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
         <v>980</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.24</v>
+        <v>5.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.48</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.48</v>
+        <v>1.76</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.95</v>
+        <v>3.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.04</v>
+        <v>4.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.48</v>
+        <v>1.76</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.48</v>
+        <v>1.58</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1939,91 +1939,91 @@
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
         <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
         <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,66 +2032,66 @@
         <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>42</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>50</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>27</v>
+        <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>42</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Dynamo Kiev</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Obolon-Brovar Kiev</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>FK Sumqayit</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arges Pitesti</t>
+          <t>Shamakhi FK</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I10" t="n">
         <v>4.9</v>
       </c>
-      <c r="I10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Hungarian NB I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Diosgyori</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>1.59</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>1.77</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>980</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR13" t="n">
         <v>4.4</v>
       </c>
-      <c r="J13" t="n">
+      <c r="AS13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU13" t="n">
         <v>3.25</v>
       </c>
-      <c r="K13" t="n">
+      <c r="AV13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY13" t="n">
         <v>3.8</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,378 +3071,4452 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LKP Motor Lublin</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.04</v>
       </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K14" t="n">
-        <v>950</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Czech 2 Liga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Vysocina Jihlava</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MFK Chrudim</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Turkish Super League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fatih Karagumruk Istanbul</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>390</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>240</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Slavia Sofia</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rapid Vienna (Am)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SKU Amstetten</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X18" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WSC Hertha Wels</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>KSV 1919</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Czech 2 Liga</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Usti Nad Labem</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FK Pribram</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>German Bundesliga 2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>German Bundesliga 2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FC Magdeburg</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SV Darmstadt</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Portuguese Segunda Liga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon B</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Danish Superliga</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>German 3 Liga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cottbus</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>B93 Copenhagen</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>HB Koge</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lyngby</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Middelfart</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Arges Pitesti</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hungarian NB I</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Gyori</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MTK Budapest</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Al-Quadisiya (KSA)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Al Riyadh SC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Radomiak Radom</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Legia Warsaw</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Polish I Liga</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Wisla Krakow</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Miedz Legnica</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K35" t="n">
+        <v>950</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Lanus</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F36" t="n">
         <v>2.02</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="G36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H36" t="n">
         <v>4.5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I36" t="n">
         <v>5.1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J36" t="n">
         <v>3.1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K36" t="n">
         <v>3.3</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2.74</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-03-11 13:05:31</t>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH82"/>
+  <dimension ref="A1:BH84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,7 +796,7 @@
         <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.71</v>
@@ -817,7 +817,7 @@
         <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -832,7 +832,7 @@
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF2" t="n">
         <v>24</v>
@@ -862,10 +862,10 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -895,19 +895,19 @@
         <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
         <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
         <v>9</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
         <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
@@ -975,16 +975,16 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>1.43</v>
@@ -999,10 +999,10 @@
         <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
         <v>19.5</v>
@@ -1056,7 +1056,7 @@
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP3" t="n">
         <v>15</v>
@@ -1068,7 +1068,7 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1083,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY3" t="n">
         <v>11.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I4" t="n">
         <v>2.66</v>
@@ -1160,7 +1160,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1942,7 +1942,7 @@
         <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
         <v>2.78</v>
@@ -1951,10 +1951,10 @@
         <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
         <v>1.21</v>
@@ -1963,16 +1963,16 @@
         <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
         <v>11.5</v>
@@ -1981,13 +1981,13 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
         <v>8.4</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
         <v>40</v>
@@ -2071,7 +2071,7 @@
         <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
         <v>5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
         <v>2.94</v>
@@ -2321,7 +2321,7 @@
         <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="K10" t="n">
         <v>5.1</v>
@@ -2360,7 +2360,7 @@
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
         <v>1.61</v>
@@ -2802,7 +2802,7 @@
         <v>980</v>
       </c>
       <c r="AO12" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
@@ -2814,7 +2814,7 @@
         <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="AT12" t="n">
         <v>9.199999999999999</v>
@@ -2826,7 +2826,7 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="AX12" t="n">
         <v>13</v>
@@ -2838,16 +2838,16 @@
         <v>7.2</v>
       </c>
       <c r="BA12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD12" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.6</v>
       </c>
       <c r="BE12" t="n">
         <v>10</v>
@@ -2856,11 +2856,11 @@
         <v>19</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
         <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
         <v>1.8</v>
@@ -2948,25 +2948,25 @@
         <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="AF13" t="n">
         <v>100</v>
@@ -2975,13 +2975,13 @@
         <v>980</v>
       </c>
       <c r="AH13" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
         <v>980</v>
       </c>
       <c r="AJ13" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="AK13" t="n">
         <v>180</v>
@@ -2999,7 +2999,7 @@
         <v>6.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.6</v>
@@ -3011,50 +3011,50 @@
         <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AU13" t="n">
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AZ13" t="n">
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BG13" t="n">
         <v>4.9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
         <v>1.89</v>
@@ -3193,7 +3193,7 @@
         <v>65</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="AQ14" t="n">
         <v>3.65</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.36</v>
       </c>
       <c r="G15" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
         <v>2.78</v>
@@ -3315,7 +3315,7 @@
         <v>1.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>1.65</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3509,16 +3509,16 @@
         <v>1.67</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="T16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
         <v>2.2</v>
@@ -3581,10 +3581,10 @@
         <v>10</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR16" t="n">
         <v>9.199999999999999</v>
@@ -3593,13 +3593,13 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
         <v>13</v>
@@ -3611,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>4.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>1.92</v>
       </c>
       <c r="G18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
         <v>3.45</v>
@@ -3900,19 +3900,19 @@
         <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U18" t="n">
         <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4103,10 +4103,10 @@
         <v>1.78</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O20" t="n">
         <v>1.39</v>
@@ -4282,7 +4282,7 @@
         <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
         <v>1.26</v>
@@ -4294,7 +4294,7 @@
         <v>1.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V20" t="n">
         <v>1.31</v>
@@ -4357,62 +4357,62 @@
         <v>75</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW20" t="n">
         <v>6</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AX20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY20" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD20" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>4.7</v>
       </c>
       <c r="G21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I21" t="n">
         <v>1.82</v>
@@ -4470,7 +4470,7 @@
         <v>2.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P21" t="n">
         <v>2.4</v>
@@ -4488,7 +4488,7 @@
         <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V21" t="n">
         <v>2.2</v>
@@ -4548,10 +4548,10 @@
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.06</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.6</v>
@@ -4560,53 +4560,53 @@
         <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.4</v>
+        <v>2.46</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.06</v>
+        <v>13.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>2.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.14</v>
+        <v>2.74</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="BE21" t="n">
-        <v>48</v>
+        <v>2.86</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.24</v>
+        <v>5.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G22" t="n">
         <v>2.66</v>
@@ -4646,10 +4646,10 @@
         <v>2.68</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
@@ -4694,28 +4694,28 @@
         <v>32</v>
       </c>
       <c r="Y22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AB22" t="n">
         <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -4727,7 +4727,7 @@
         <v>980</v>
       </c>
       <c r="AJ22" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
         <v>24</v>
@@ -4754,7 +4754,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
         <v>15.5</v>
@@ -4766,7 +4766,7 @@
         <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
         <v>19</v>
@@ -4778,29 +4778,29 @@
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BB22" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
         <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>2.62</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
         <v>2.84</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -4849,7 +4849,7 @@
         <v>3.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4867,10 +4867,10 @@
         <v>1.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
         <v>1.84</v>
@@ -4879,10 +4879,10 @@
         <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
         <v>14.5</v>
@@ -4939,7 +4939,7 @@
         <v>46</v>
       </c>
       <c r="AP23" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>9.199999999999999</v>
@@ -4963,13 +4963,13 @@
         <v>3.85</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
         <v>3.95</v>
@@ -4978,13 +4978,13 @@
         <v>3.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.8</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
         <v>3.8</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.12</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AS24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW24" t="n">
         <v>2.02</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AX24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.93</v>
       </c>
-      <c r="AU24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         <v>6.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
         <v>1.03</v>
@@ -5273,7 +5273,7 @@
         <v>3.45</v>
       </c>
       <c r="X25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y25" t="n">
         <v>38</v>
@@ -5291,7 +5291,7 @@
         <v>13.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AE25" t="n">
         <v>200</v>
@@ -5303,7 +5303,7 @@
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AI25" t="n">
         <v>160</v>
@@ -5315,13 +5315,13 @@
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AM25" t="n">
         <v>180</v>
       </c>
       <c r="AN25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO25" t="n">
         <v>250</v>
@@ -5330,13 +5330,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5345,10 +5345,10 @@
         <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX25" t="n">
         <v>7.4</v>
@@ -5357,10 +5357,10 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB25" t="n">
         <v>9.4</v>
@@ -5369,20 +5369,20 @@
         <v>12</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF25" t="n">
         <v>4</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>11.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
         <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="R27" t="n">
         <v>1.41</v>
@@ -5649,10 +5649,10 @@
         <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V27" t="n">
         <v>1.79</v>
@@ -5712,65 +5712,65 @@
         <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="AX27" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.12</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -5909,52 +5909,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6037,16 +6037,16 @@
         <v>2.52</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V29" t="n">
         <v>1.21</v>
       </c>
       <c r="W29" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X29" t="n">
         <v>26</v>
@@ -6097,68 +6097,68 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="AU29" t="n">
         <v>7.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6207,13 +6207,13 @@
         <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="O30" t="n">
         <v>1.4</v>
@@ -6297,52 +6297,52 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6407,16 +6407,16 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O31" t="n">
         <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="R31" t="n">
         <v>1.22</v>
@@ -6491,52 +6491,52 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>1.81</v>
       </c>
       <c r="G32" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="H32" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="K32" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6601,16 +6601,16 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="O32" t="n">
         <v>1.38</v>
       </c>
       <c r="P32" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>1.38</v>
       </c>
       <c r="R32" t="n">
         <v>1.22</v>
@@ -6625,10 +6625,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W32" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6685,52 +6685,52 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>3.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
@@ -6879,52 +6879,52 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7073,52 +7073,52 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
         <v>1.01</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7177,28 +7177,28 @@
         <v>3.9</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
         <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7267,52 +7267,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7377,13 +7377,13 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O36" t="n">
         <v>1.34</v>
       </c>
       <c r="P36" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q36" t="n">
         <v>1.96</v>
@@ -7461,52 +7461,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
         <v>2.04</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7601,7 +7601,7 @@
         <v>1.55</v>
       </c>
       <c r="X37" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
         <v>15.5</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AQ37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BD37" t="n">
         <v>2.28</v>
       </c>
-      <c r="AR37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AT37" t="n">
+      <c r="BE37" t="n">
         <v>2.32</v>
       </c>
-      <c r="AU37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BF37" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>4.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -7786,7 +7786,7 @@
         <v>1.83</v>
       </c>
       <c r="U38" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>1.17</v>
@@ -7801,7 +7801,7 @@
         <v>26</v>
       </c>
       <c r="Z38" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA38" t="n">
         <v>210</v>
@@ -7855,7 +7855,7 @@
         <v>19</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS38" t="n">
         <v>6.2</v>
@@ -7882,7 +7882,7 @@
         <v>18</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB38" t="n">
         <v>13</v>
@@ -7894,7 +7894,7 @@
         <v>5.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF38" t="n">
         <v>6.2</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -7977,10 +7977,10 @@
         <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="U39" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="V39" t="n">
         <v>1.5</v>
@@ -7992,34 +7992,34 @@
         <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA39" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB39" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD39" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE39" t="n">
         <v>38</v>
       </c>
       <c r="AF39" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG39" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH39" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI39" t="n">
         <v>55</v>
@@ -8052,7 +8052,7 @@
         <v>6.8</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AT39" t="n">
         <v>5.2</v>
@@ -8064,41 +8064,41 @@
         <v>5.9</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AY39" t="n">
         <v>5.9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BF39" t="n">
-        <v>26</v>
+        <v>8.4</v>
       </c>
       <c r="BG39" t="n">
         <v>8.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -8171,10 +8171,10 @@
         <v>5.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="V40" t="n">
         <v>1.27</v>
@@ -8201,7 +8201,7 @@
         <v>7.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE40" t="n">
         <v>100</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
         <v>1.42</v>
       </c>
       <c r="W41" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8431,52 +8431,52 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
         <v>1.01</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8520,13 @@
         <v>2.58</v>
       </c>
       <c r="G42" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H42" t="n">
         <v>2.62</v>
       </c>
       <c r="I42" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>3.2</v>
@@ -8565,10 +8565,10 @@
         <v>2.16</v>
       </c>
       <c r="V42" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W42" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X42" t="n">
         <v>21</v>
@@ -8601,7 +8601,7 @@
         <v>14.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI42" t="n">
         <v>42</v>
@@ -8625,7 +8625,7 @@
         <v>24</v>
       </c>
       <c r="AP42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ42" t="n">
         <v>3.8</v>
@@ -8655,16 +8655,16 @@
         <v>3.75</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BA42" t="n">
         <v>4.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD42" t="n">
         <v>4.5</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -8768,25 +8768,25 @@
         <v>24</v>
       </c>
       <c r="Y43" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z43" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AA43" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AB43" t="n">
         <v>28</v>
       </c>
       <c r="AC43" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD43" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE43" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AF43" t="n">
         <v>65</v>
@@ -8828,7 +8828,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT43" t="n">
         <v>6.4</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -9013,52 +9013,52 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -9123,10 +9123,10 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>6.4</v>
       </c>
       <c r="O45" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P45" t="n">
         <v>2.88</v>
@@ -9135,16 +9135,16 @@
         <v>1.42</v>
       </c>
       <c r="R45" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="S45" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V45" t="n">
         <v>1.16</v>
@@ -9201,68 +9201,68 @@
         <v>95</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.04</v>
+        <v>2.98</v>
       </c>
       <c r="AT45" t="n">
         <v>10.5</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AW45" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.89</v>
+        <v>2.68</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.99</v>
+        <v>2.86</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="BC45" t="n">
         <v>10</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="BE45" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="BF45" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="BG45" t="n">
-        <v>2.04</v>
+        <v>2.98</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -9335,10 +9335,10 @@
         <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V46" t="n">
         <v>1.25</v>
@@ -9347,116 +9347,116 @@
         <v>2</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB46" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AC46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG46" t="n">
         <v>11</v>
       </c>
-      <c r="AD46" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE46" t="n">
+      <c r="AH46" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI46" t="n">
         <v>100</v>
       </c>
-      <c r="AF46" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ46" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AK46" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AL46" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.24</v>
+        <v>9.6</v>
       </c>
       <c r="AQ46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX46" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR46" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AY46" t="n">
-        <v>1.94</v>
+        <v>9</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2.08</v>
+        <v>18.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.24</v>
+        <v>7.6</v>
       </c>
       <c r="BB46" t="n">
-        <v>2.08</v>
+        <v>18.5</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.08</v>
+        <v>19</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.16</v>
+        <v>7</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="BF46" t="n">
-        <v>2.24</v>
+        <v>13</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.24</v>
+        <v>7.8</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -9478,31 +9478,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.87</v>
+        <v>3.05</v>
       </c>
       <c r="G47" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="H47" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>2.36</v>
       </c>
       <c r="J47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,146 +9511,146 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="O47" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P47" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R47" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="S47" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="T47" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="U47" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="W47" t="n">
-        <v>1.94</v>
+        <v>1.37</v>
       </c>
       <c r="X47" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y47" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z47" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA47" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD47" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE47" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG47" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH47" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM47" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO47" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ47" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS47" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT47" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU47" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV47" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW47" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX47" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY47" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ47" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA47" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB47" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC47" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD47" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE47" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG47" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -9684,16 +9684,16 @@
         <v>2.46</v>
       </c>
       <c r="G48" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="H48" t="n">
         <v>2.5</v>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J48" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K48" t="n">
         <v>4.6</v>
@@ -9714,7 +9714,7 @@
         <v>2.68</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R48" t="n">
         <v>1.58</v>
@@ -9789,52 +9789,52 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF48" t="n">
         <v>1.01</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>4.1</v>
       </c>
       <c r="H49" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I49" t="n">
         <v>2.08</v>
@@ -9911,16 +9911,16 @@
         <v>1.58</v>
       </c>
       <c r="R49" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S49" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="T49" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="U49" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="V49" t="n">
         <v>1.92</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -10177,52 +10177,52 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
         <v>1.01</v>
@@ -10232,14 +10232,14 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10254,186 +10254,186 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="F51" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G51" t="n">
         <v>3.05</v>
       </c>
-      <c r="G51" t="n">
-        <v>3.9</v>
-      </c>
       <c r="H51" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="I51" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K51" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M51" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O51" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="P51" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="R51" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V51" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W51" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10448,179 +10448,179 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="G52" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="H52" t="n">
-        <v>2.46</v>
+        <v>3.45</v>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K52" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="L52" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X52" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS52" t="n">
         <v>4.8</v>
       </c>
-      <c r="O52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X52" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="AT52" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG52" t="n">
         <v>16</v>
       </c>
-      <c r="AC52" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         <v>2.22</v>
       </c>
       <c r="G53" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H53" t="n">
         <v>2.9</v>
@@ -10687,16 +10687,16 @@
         <v>1.45</v>
       </c>
       <c r="R53" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T53" t="n">
         <v>1.45</v>
       </c>
       <c r="U53" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="V53" t="n">
         <v>1.47</v>
@@ -10765,7 +10765,7 @@
         <v>18.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS53" t="n">
         <v>6.8</v>
@@ -10780,7 +10780,7 @@
         <v>12</v>
       </c>
       <c r="AW53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX53" t="n">
         <v>17.5</v>
@@ -10792,7 +10792,7 @@
         <v>12</v>
       </c>
       <c r="BA53" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BB53" t="n">
         <v>6.4</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -10851,7 +10851,7 @@
         <v>1.75</v>
       </c>
       <c r="H54" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I54" t="n">
         <v>5.4</v>
@@ -10869,10 +10869,10 @@
         <v>1.02</v>
       </c>
       <c r="N54" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="O54" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P54" t="n">
         <v>2.7</v>
@@ -10881,16 +10881,16 @@
         <v>1.5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="S54" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U54" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V54" t="n">
         <v>1.25</v>
@@ -10899,116 +10899,116 @@
         <v>2.32</v>
       </c>
       <c r="X54" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y54" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Z54" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AA54" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB54" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC54" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AD54" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE54" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF54" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG54" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH54" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AI54" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ54" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AK54" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AL54" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AM54" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN54" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO54" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.79</v>
+        <v>2.84</v>
       </c>
       <c r="AR54" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW54" t="n">
         <v>1.83</v>
       </c>
-      <c r="AS54" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AX54" t="n">
-        <v>1.71</v>
+        <v>5.9</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.89</v>
+        <v>4</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -11075,13 +11075,13 @@
         <v>1.48</v>
       </c>
       <c r="R55" t="n">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="S55" t="n">
         <v>2.12</v>
       </c>
       <c r="T55" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U55" t="n">
         <v>2.28</v>
@@ -11144,65 +11144,65 @@
         <v>1000</v>
       </c>
       <c r="AO55" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.93</v>
+        <v>2.54</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.74</v>
+        <v>2.22</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.93</v>
+        <v>2.54</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.93</v>
+        <v>2.54</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.93</v>
+        <v>3.85</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -11284,7 +11284,7 @@
         <v>1.27</v>
       </c>
       <c r="W56" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11341,52 +11341,52 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF56" t="n">
         <v>1.01</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -11427,10 +11427,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G57" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H57" t="n">
         <v>2.62</v>
@@ -11469,16 +11469,16 @@
         <v>2.2</v>
       </c>
       <c r="T57" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="U57" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="V57" t="n">
         <v>1.54</v>
       </c>
       <c r="W57" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X57" t="n">
         <v>34</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
         <v>3.65</v>
       </c>
       <c r="K58" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11663,10 +11663,10 @@
         <v>2.94</v>
       </c>
       <c r="T58" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U58" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V58" t="n">
         <v>1.33</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G59" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H59" t="n">
         <v>4.2</v>
@@ -11827,19 +11827,19 @@
         <v>4.4</v>
       </c>
       <c r="J59" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K59" t="n">
         <v>3.55</v>
       </c>
       <c r="L59" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M59" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>1.43</v>
@@ -11857,37 +11857,37 @@
         <v>4.4</v>
       </c>
       <c r="T59" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U59" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V59" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W59" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X59" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y59" t="n">
         <v>12.5</v>
       </c>
       <c r="Z59" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA59" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB59" t="n">
         <v>8</v>
       </c>
       <c r="AC59" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD59" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE59" t="n">
         <v>65</v>
@@ -11896,10 +11896,10 @@
         <v>11.5</v>
       </c>
       <c r="AG59" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH59" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI59" t="n">
         <v>80</v>
@@ -11911,31 +11911,31 @@
         <v>25</v>
       </c>
       <c r="AL59" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM59" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN59" t="n">
         <v>20</v>
       </c>
       <c r="AO59" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP59" t="n">
         <v>10</v>
       </c>
       <c r="AQ59" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR59" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS59" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AT59" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU59" t="n">
         <v>7.2</v>
@@ -11947,38 +11947,38 @@
         <v>50</v>
       </c>
       <c r="AX59" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY59" t="n">
         <v>10</v>
       </c>
       <c r="AZ59" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA59" t="n">
         <v>34</v>
       </c>
       <c r="BB59" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD59" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BE59" t="n">
         <v>44</v>
       </c>
       <c r="BF59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG59" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G60" t="n">
         <v>1.84</v>
@@ -12051,10 +12051,10 @@
         <v>3.1</v>
       </c>
       <c r="T60" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U60" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V60" t="n">
         <v>1.18</v>
@@ -12066,31 +12066,31 @@
         <v>1000</v>
       </c>
       <c r="Y60" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z60" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA60" t="n">
         <v>1000</v>
       </c>
       <c r="AB60" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC60" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD60" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE60" t="n">
         <v>1000</v>
       </c>
       <c r="AF60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG60" t="n">
         <v>13</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>13.5</v>
       </c>
       <c r="AH60" t="n">
         <v>30</v>
@@ -12099,80 +12099,80 @@
         <v>1000</v>
       </c>
       <c r="AJ60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK60" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL60" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM60" t="n">
         <v>1000</v>
       </c>
       <c r="AN60" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO60" t="n">
         <v>1000</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="AQ60" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU60" t="n">
         <v>2.2</v>
       </c>
-      <c r="AR60" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV60" t="n">
-        <v>2.24</v>
+        <v>18</v>
       </c>
       <c r="AW60" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="AX60" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AY60" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="AZ60" t="n">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="BA60" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="BB60" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="BC60" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="BD60" t="n">
-        <v>2.32</v>
+        <v>2.76</v>
       </c>
       <c r="BE60" t="n">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="BF60" t="n">
-        <v>2.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG60" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12236,7 @@
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R61" t="n">
         <v>1.12</v>
@@ -12311,52 +12311,52 @@
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ61" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR61" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS61" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AT61" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU61" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV61" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW61" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX61" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY61" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ61" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA61" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB61" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BC61" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD61" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE61" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF61" t="n">
         <v>1.01</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -12403,10 +12403,10 @@
         <v>1.72</v>
       </c>
       <c r="H62" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>4</v>
@@ -12505,52 +12505,52 @@
         <v>1000</v>
       </c>
       <c r="AP62" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ62" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AR62" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AS62" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT62" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU62" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV62" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW62" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX62" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY62" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ62" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA62" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB62" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC62" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD62" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BE62" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF62" t="n">
         <v>1.01</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -12633,10 +12633,10 @@
         <v>3.85</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V63" t="n">
         <v>1.41</v>
@@ -12663,13 +12663,13 @@
         <v>8.4</v>
       </c>
       <c r="AD63" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE63" t="n">
         <v>50</v>
       </c>
       <c r="AF63" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG63" t="n">
         <v>14.5</v>
@@ -12699,7 +12699,7 @@
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AQ63" t="n">
         <v>8.800000000000001</v>
@@ -12711,7 +12711,7 @@
         <v>36</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AU63" t="n">
         <v>6.2</v>
@@ -12720,19 +12720,19 @@
         <v>10</v>
       </c>
       <c r="AW63" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AX63" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AY63" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AZ63" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BA63" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB63" t="n">
         <v>3.75</v>
@@ -12741,20 +12741,20 @@
         <v>3.7</v>
       </c>
       <c r="BD63" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE63" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF63" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG63" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -12893,52 +12893,52 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ64" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR64" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS64" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="AT64" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU64" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV64" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW64" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX64" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY64" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ64" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA64" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB64" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC64" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD64" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE64" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF64" t="n">
         <v>1.01</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -12979,28 +12979,28 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G65" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H65" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I65" t="n">
         <v>4.1</v>
       </c>
       <c r="J65" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K65" t="n">
         <v>3.15</v>
       </c>
       <c r="L65" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M65" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N65" t="n">
         <v>3</v>
@@ -13012,7 +13012,7 @@
         <v>1.67</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R65" t="n">
         <v>1.25</v>
@@ -13033,7 +13033,7 @@
         <v>1.74</v>
       </c>
       <c r="X65" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y65" t="n">
         <v>12</v>
@@ -13054,10 +13054,10 @@
         <v>16.5</v>
       </c>
       <c r="AE65" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF65" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG65" t="n">
         <v>11.5</v>
@@ -13075,13 +13075,13 @@
         <v>28</v>
       </c>
       <c r="AL65" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM65" t="n">
         <v>140</v>
       </c>
       <c r="AN65" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO65" t="n">
         <v>70</v>
@@ -13090,7 +13090,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ65" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR65" t="n">
         <v>23</v>
@@ -13105,13 +13105,13 @@
         <v>6.6</v>
       </c>
       <c r="AV65" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW65" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX65" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY65" t="n">
         <v>10.5</v>
@@ -13120,7 +13120,7 @@
         <v>19</v>
       </c>
       <c r="BA65" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BB65" t="n">
         <v>27</v>
@@ -13142,14 +13142,14 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13164,31 +13164,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Morton</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="G66" t="n">
-        <v>5.8</v>
+        <v>2.68</v>
       </c>
       <c r="H66" t="n">
-        <v>1.87</v>
+        <v>3.15</v>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J66" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="K66" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -13197,22 +13197,22 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O66" t="n">
         <v>1.35</v>
       </c>
       <c r="P66" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="R66" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S66" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T66" t="n">
         <v>1.01</v>
@@ -13221,10 +13221,10 @@
         <v>1.01</v>
       </c>
       <c r="V66" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="W66" t="n">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="X66" t="n">
         <v>1000</v>
@@ -13281,52 +13281,52 @@
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ66" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR66" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS66" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT66" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU66" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV66" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW66" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX66" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY66" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ66" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA66" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BB66" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC66" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD66" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE66" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF66" t="n">
         <v>1.01</v>
@@ -13336,14 +13336,14 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13358,31 +13358,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Morton</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="G67" t="n">
-        <v>2.68</v>
+        <v>5.8</v>
       </c>
       <c r="H67" t="n">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="I67" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="K67" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -13391,22 +13391,22 @@
         <v>1.01</v>
       </c>
       <c r="N67" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O67" t="n">
         <v>1.35</v>
       </c>
       <c r="P67" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q67" t="n">
         <v>1.92</v>
       </c>
       <c r="R67" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S67" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T67" t="n">
         <v>1.01</v>
@@ -13415,10 +13415,10 @@
         <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="W67" t="n">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -13475,52 +13475,52 @@
         <v>1000</v>
       </c>
       <c r="AP67" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ67" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR67" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS67" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT67" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU67" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV67" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW67" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX67" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY67" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ67" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA67" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB67" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC67" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD67" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE67" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BF67" t="n">
         <v>1.01</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -13603,10 +13603,10 @@
         <v>4.1</v>
       </c>
       <c r="T68" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U68" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="V68" t="n">
         <v>1.15</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -13797,10 +13797,10 @@
         <v>2.84</v>
       </c>
       <c r="T69" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U69" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V69" t="n">
         <v>1.3</v>
@@ -13863,16 +13863,16 @@
         <v>1000</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AR69" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AS69" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AT69" t="n">
         <v>8.199999999999999</v>
@@ -13881,44 +13881,44 @@
         <v>7.2</v>
       </c>
       <c r="AV69" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AW69" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AX69" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AY69" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AZ69" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BA69" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BB69" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BC69" t="n">
         <v>2.06</v>
       </c>
-      <c r="BC69" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BD69" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BE69" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BF69" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BG69" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -13940,179 +13940,179 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.23</v>
+        <v>2.58</v>
       </c>
       <c r="G70" t="n">
-        <v>1.43</v>
+        <v>2.98</v>
       </c>
       <c r="H70" t="n">
-        <v>8.6</v>
+        <v>2.68</v>
       </c>
       <c r="I70" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
       </c>
       <c r="M70" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N70" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="O70" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="P70" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="R70" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S70" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T70" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U70" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V70" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="W70" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="X70" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y70" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z70" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA70" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB70" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC70" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD70" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE70" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF70" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG70" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH70" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI70" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ70" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK70" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL70" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM70" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN70" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO70" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP70" t="n">
-        <v>17</v>
+        <v>3.35</v>
       </c>
       <c r="AQ70" t="n">
-        <v>26</v>
+        <v>3.25</v>
       </c>
       <c r="AR70" t="n">
-        <v>50</v>
+        <v>3.6</v>
       </c>
       <c r="AS70" t="n">
-        <v>50</v>
+        <v>3.95</v>
       </c>
       <c r="AT70" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="AU70" t="n">
-        <v>9.800000000000001</v>
+        <v>2.94</v>
       </c>
       <c r="AV70" t="n">
-        <v>30</v>
+        <v>3.35</v>
       </c>
       <c r="AW70" t="n">
-        <v>50</v>
+        <v>3.85</v>
       </c>
       <c r="AX70" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="AY70" t="n">
-        <v>9</v>
+        <v>3.35</v>
       </c>
       <c r="AZ70" t="n">
-        <v>27</v>
+        <v>3.55</v>
       </c>
       <c r="BA70" t="n">
-        <v>50</v>
+        <v>3.95</v>
       </c>
       <c r="BB70" t="n">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="BC70" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="BD70" t="n">
-        <v>32</v>
+        <v>3.95</v>
       </c>
       <c r="BE70" t="n">
-        <v>50</v>
+        <v>4.1</v>
       </c>
       <c r="BF70" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG70" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G71" t="n">
         <v>2.72</v>
@@ -14152,13 +14152,13 @@
         <v>3.05</v>
       </c>
       <c r="I71" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K71" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14191,7 +14191,7 @@
         <v>1.01</v>
       </c>
       <c r="V71" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W71" t="n">
         <v>1.58</v>
@@ -14251,52 +14251,52 @@
         <v>1000</v>
       </c>
       <c r="AP71" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ71" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR71" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS71" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT71" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU71" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV71" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW71" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AX71" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY71" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ71" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA71" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB71" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC71" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD71" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE71" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF71" t="n">
         <v>1.01</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="G72" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H72" t="n">
         <v>2.82</v>
       </c>
       <c r="I72" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>3.2</v>
       </c>
       <c r="K72" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -14385,10 +14385,10 @@
         <v>1.01</v>
       </c>
       <c r="V72" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W72" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14445,52 +14445,52 @@
         <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ72" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR72" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS72" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT72" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU72" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV72" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW72" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX72" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY72" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ72" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA72" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB72" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC72" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD72" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE72" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF72" t="n">
         <v>1.01</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -14522,31 +14522,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.58</v>
+        <v>1.25</v>
       </c>
       <c r="G73" t="n">
-        <v>2.98</v>
+        <v>1.43</v>
       </c>
       <c r="H73" t="n">
-        <v>2.68</v>
+        <v>8.6</v>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14555,22 +14555,22 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="O73" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="P73" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="R73" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T73" t="n">
         <v>1.01</v>
@@ -14579,10 +14579,10 @@
         <v>1.01</v>
       </c>
       <c r="V73" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -14639,52 +14639,52 @@
         <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ73" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR73" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS73" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT73" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU73" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV73" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW73" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX73" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY73" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ73" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA73" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BB73" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC73" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD73" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE73" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF73" t="n">
         <v>1.01</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G74" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H74" t="n">
         <v>7.6</v>
@@ -14737,10 +14737,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K74" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L74" t="n">
         <v>1.33</v>
@@ -14749,13 +14749,13 @@
         <v>1.05</v>
       </c>
       <c r="N74" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O74" t="n">
         <v>1.26</v>
       </c>
       <c r="P74" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q74" t="n">
         <v>1.76</v>
@@ -14773,10 +14773,10 @@
         <v>1.96</v>
       </c>
       <c r="V74" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W74" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X74" t="n">
         <v>20</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -14922,16 +14922,16 @@
         <v>2.66</v>
       </c>
       <c r="G75" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H75" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J75" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K75" t="n">
         <v>6.8</v>
@@ -14967,10 +14967,10 @@
         <v>1.01</v>
       </c>
       <c r="V75" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W75" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X75" t="n">
         <v>1000</v>
@@ -15027,52 +15027,52 @@
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ75" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR75" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS75" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AT75" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU75" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV75" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW75" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX75" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY75" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ75" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA75" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BB75" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC75" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD75" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE75" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF75" t="n">
         <v>1.01</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -15137,16 +15137,16 @@
         <v>1.01</v>
       </c>
       <c r="N76" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O76" t="n">
         <v>1.3</v>
       </c>
       <c r="P76" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R76" t="n">
         <v>1.27</v>
@@ -15221,52 +15221,52 @@
         <v>1000</v>
       </c>
       <c r="AP76" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ76" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR76" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS76" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT76" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU76" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV76" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW76" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX76" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AY76" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ76" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA76" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB76" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BC76" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BD76" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE76" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF76" t="n">
         <v>1.01</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15322,7 @@
         <v>3.55</v>
       </c>
       <c r="K77" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L77" t="n">
         <v>1.42</v>
@@ -15331,7 +15331,7 @@
         <v>1.08</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O77" t="n">
         <v>1.37</v>
@@ -15340,7 +15340,7 @@
         <v>1.85</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R77" t="n">
         <v>1.32</v>
@@ -15358,7 +15358,7 @@
         <v>1.78</v>
       </c>
       <c r="W77" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X77" t="n">
         <v>13</v>
@@ -15421,7 +15421,7 @@
         <v>8.6</v>
       </c>
       <c r="AR77" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS77" t="n">
         <v>26</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -15492,12 +15492,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -15513,22 +15513,22 @@
         <v>1000</v>
       </c>
       <c r="J78" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K78" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P78" t="n">
         <v>1.24</v>
@@ -15537,134 +15537,134 @@
         <v>1.01</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO78" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG78" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -15686,12 +15686,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -15707,158 +15707,158 @@
         <v>1000</v>
       </c>
       <c r="J79" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K79" t="n">
         <v>1000</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P79" t="n">
         <v>1.24</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG79" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -15880,12 +15880,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -15901,22 +15901,22 @@
         <v>1000</v>
       </c>
       <c r="J80" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K80" t="n">
         <v>1000</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P80" t="n">
         <v>1.24</v>
@@ -15925,134 +15925,134 @@
         <v>1.01</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
@@ -16074,12 +16074,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MC El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Olympique Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -16095,352 +16095,740 @@
         <v>1000</v>
       </c>
       <c r="J81" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K81" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P81" t="n">
         <v>1.24</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-11 17:30:13</t>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Deportes Recoleta</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Union San Felipe</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S82" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH82" t="inlineStr">
+        <is>
+          <t>2026-03-11 19:44:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Estudiantes</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Lanus</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G82" t="n">
+      <c r="F83" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G83" t="n">
         <v>2.2</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H83" t="n">
         <v>4.5</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I83" t="n">
         <v>5.1</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J83" t="n">
         <v>3.1</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K83" t="n">
         <v>3.3</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L83" t="n">
         <v>0</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M83" t="n">
         <v>0</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N83" t="n">
         <v>0</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="P82" t="n">
+      <c r="P83" t="n">
         <v>1.46</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="Q83" t="n">
         <v>2.78</v>
       </c>
-      <c r="R82" t="n">
+      <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="n">
+      <c r="S83" t="n">
         <v>0</v>
       </c>
-      <c r="T82" t="n">
+      <c r="T83" t="n">
         <v>0</v>
       </c>
-      <c r="U82" t="n">
+      <c r="U83" t="n">
         <v>0</v>
       </c>
-      <c r="V82" t="n">
+      <c r="V83" t="n">
         <v>0</v>
       </c>
-      <c r="W82" t="n">
+      <c r="W83" t="n">
         <v>0</v>
       </c>
-      <c r="X82" t="n">
+      <c r="X83" t="n">
         <v>0</v>
       </c>
-      <c r="Y82" t="n">
+      <c r="Y83" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" t="n">
+      <c r="Z83" t="n">
         <v>0</v>
       </c>
-      <c r="AA82" t="n">
+      <c r="AA83" t="n">
         <v>0</v>
       </c>
-      <c r="AB82" t="n">
+      <c r="AB83" t="n">
         <v>0</v>
       </c>
-      <c r="AC82" t="n">
+      <c r="AC83" t="n">
         <v>0</v>
       </c>
-      <c r="AD82" t="n">
+      <c r="AD83" t="n">
         <v>0</v>
       </c>
-      <c r="AE82" t="n">
+      <c r="AE83" t="n">
         <v>0</v>
       </c>
-      <c r="AF82" t="n">
+      <c r="AF83" t="n">
         <v>0</v>
       </c>
-      <c r="AG82" t="n">
+      <c r="AG83" t="n">
         <v>0</v>
       </c>
-      <c r="AH82" t="n">
+      <c r="AH83" t="n">
         <v>0</v>
       </c>
-      <c r="AI82" t="n">
+      <c r="AI83" t="n">
         <v>0</v>
       </c>
-      <c r="AJ82" t="n">
+      <c r="AJ83" t="n">
         <v>0</v>
       </c>
-      <c r="AK82" t="n">
+      <c r="AK83" t="n">
         <v>0</v>
       </c>
-      <c r="AL82" t="n">
+      <c r="AL83" t="n">
         <v>0</v>
       </c>
-      <c r="AM82" t="n">
+      <c r="AM83" t="n">
         <v>0</v>
       </c>
-      <c r="AN82" t="n">
+      <c r="AN83" t="n">
         <v>0</v>
       </c>
-      <c r="AO82" t="n">
+      <c r="AO83" t="n">
         <v>0</v>
       </c>
-      <c r="AP82" t="n">
+      <c r="AP83" t="n">
         <v>0</v>
       </c>
-      <c r="AQ82" t="n">
+      <c r="AQ83" t="n">
         <v>0</v>
       </c>
-      <c r="AR82" t="n">
+      <c r="AR83" t="n">
         <v>0</v>
       </c>
-      <c r="AS82" t="n">
+      <c r="AS83" t="n">
         <v>0</v>
       </c>
-      <c r="AT82" t="n">
+      <c r="AT83" t="n">
         <v>0</v>
       </c>
-      <c r="AU82" t="n">
+      <c r="AU83" t="n">
         <v>0</v>
       </c>
-      <c r="AV82" t="n">
+      <c r="AV83" t="n">
         <v>0</v>
       </c>
-      <c r="AW82" t="n">
+      <c r="AW83" t="n">
         <v>0</v>
       </c>
-      <c r="AX82" t="n">
+      <c r="AX83" t="n">
         <v>0</v>
       </c>
-      <c r="AY82" t="n">
+      <c r="AY83" t="n">
         <v>0</v>
       </c>
-      <c r="AZ82" t="n">
+      <c r="AZ83" t="n">
         <v>0</v>
       </c>
-      <c r="BA82" t="n">
+      <c r="BA83" t="n">
         <v>0</v>
       </c>
-      <c r="BB82" t="n">
+      <c r="BB83" t="n">
         <v>0</v>
       </c>
-      <c r="BC82" t="n">
+      <c r="BC83" t="n">
         <v>0</v>
       </c>
-      <c r="BD82" t="n">
+      <c r="BD83" t="n">
         <v>0</v>
       </c>
-      <c r="BE82" t="n">
+      <c r="BE83" t="n">
         <v>0</v>
       </c>
-      <c r="BF82" t="n">
+      <c r="BF83" t="n">
         <v>0</v>
       </c>
-      <c r="BG82" t="n">
+      <c r="BG83" t="n">
         <v>0</v>
       </c>
-      <c r="BH82" t="inlineStr">
-        <is>
-          <t>2026-03-11 17:30:13</t>
+      <c r="BH83" t="inlineStr">
+        <is>
+          <t>2026-03-11 19:44:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Cobreloa Calama</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K84" t="n">
+        <v>950</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>2026-03-11 19:44:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH84"/>
+  <dimension ref="A1:BH88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
         <v>2.4</v>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
@@ -874,7 +874,7 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
@@ -898,19 +898,19 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
         <v>21</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -957,46 +957,46 @@
         <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
         <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
         <v>1.72</v>
@@ -1011,19 +1011,19 @@
         <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1059,19 +1059,19 @@
         <v>18.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
@@ -1083,28 +1083,28 @@
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.8</v>
       </c>
       <c r="BD3" t="n">
         <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
         <v>20</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1169,7 +1169,7 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -1193,10 +1193,10 @@
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1262,7 +1262,7 @@
         <v>3.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT4" t="n">
         <v>3.4</v>
@@ -1274,13 +1274,13 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX4" t="n">
         <v>3.8</v>
       </c>
-      <c r="AX4" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AY4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>12.5</v>
@@ -1295,7 +1295,7 @@
         <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
         <v>4.2</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>85</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
@@ -1778,7 +1778,7 @@
         <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X7" t="n">
         <v>980</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -1969,10 +1969,10 @@
         <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
         <v>11.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.39</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2166,7 +2166,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>3.15</v>
@@ -2724,19 +2724,19 @@
         <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
         <v>1.81</v>
@@ -2751,7 +2751,7 @@
         <v>1.61</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
         <v>12</v>
@@ -2835,32 +2835,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB12" t="n">
         <v>30</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF12" t="n">
         <v>19</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="I13" t="n">
         <v>1.42</v>
@@ -2906,10 +2906,10 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -2939,34 +2939,34 @@
         <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AB13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE13" t="n">
         <v>980</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>17.5</v>
       </c>
       <c r="AF13" t="n">
         <v>100</v>
@@ -2975,7 +2975,7 @@
         <v>980</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AI13" t="n">
         <v>980</v>
@@ -2996,7 +2996,7 @@
         <v>240</v>
       </c>
       <c r="AO13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
@@ -3011,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>10</v>
@@ -3023,38 +3023,38 @@
         <v>12.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AY13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
         <v>1.89</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G15" t="n">
         <v>2.6</v>
@@ -3303,7 +3303,7 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
@@ -3312,13 +3312,13 @@
         <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3330,7 +3330,7 @@
         <v>1.46</v>
       </c>
       <c r="W15" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
         <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
         <v>1.67</v>
@@ -3584,7 +3584,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR16" t="n">
         <v>9.199999999999999</v>
@@ -3593,13 +3593,13 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AW16" t="n">
         <v>13</v>
@@ -3611,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>4.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
         <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
         <v>1.81</v>
@@ -3909,10 +3909,10 @@
         <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4058,13 +4058,13 @@
         <v>1.95</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="H19" t="n">
         <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
@@ -4073,7 +4073,7 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
         <v>2.66</v>
@@ -4646,7 +4646,7 @@
         <v>2.68</v>
       </c>
       <c r="I22" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J22" t="n">
         <v>3.85</v>
@@ -4679,13 +4679,13 @@
         <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U22" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="V22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W22" t="n">
         <v>1.6</v>
@@ -4745,7 +4745,7 @@
         <v>14.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AQ22" t="n">
         <v>16</v>
@@ -4760,7 +4760,7 @@
         <v>15.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV22" t="n">
         <v>11.5</v>
@@ -4790,7 +4790,7 @@
         <v>24</v>
       </c>
       <c r="BE22" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BF22" t="n">
         <v>11.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>2.84</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -4861,7 +4861,7 @@
         <v>1.39</v>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
         <v>1.98</v>
@@ -4870,7 +4870,7 @@
         <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
         <v>1.84</v>
@@ -4879,10 +4879,10 @@
         <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
         <v>14.5</v>
@@ -4978,7 +4978,7 @@
         <v>3.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>24</v>
+        <v>3.8</v>
       </c>
       <c r="BD23" t="n">
         <v>3.95</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
         <v>1.59</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
         <v>2.44</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -5837,10 +5837,10 @@
         <v>2.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.04</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.39</v>
@@ -6213,13 +6213,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O30" t="n">
         <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
         <v>2.08</v>
@@ -6237,10 +6237,10 @@
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W30" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>1.53</v>
       </c>
       <c r="G31" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K31" t="n">
         <v>4.5</v>
@@ -6407,16 +6407,16 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="O31" t="n">
         <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="R31" t="n">
         <v>1.22</v>
@@ -6428,13 +6428,13 @@
         <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V31" t="n">
         <v>1.11</v>
       </c>
       <c r="W31" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6586,10 +6586,10 @@
         <v>3.75</v>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="K32" t="n">
         <v>5.5</v>
@@ -6610,19 +6610,19 @@
         <v>1.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="R32" t="n">
         <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V32" t="n">
         <v>1.19</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>1.98</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H33" t="n">
         <v>3.35</v>
@@ -6783,7 +6783,7 @@
         <v>4.8</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
         <v>3.55</v>
@@ -6795,19 +6795,19 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O33" t="n">
         <v>1.02</v>
       </c>
       <c r="P33" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
         <v>3.7</v>
@@ -6816,13 +6816,13 @@
         <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V33" t="n">
         <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
         <v>3.9</v>
       </c>
       <c r="L35" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
@@ -7192,7 +7192,7 @@
         <v>1.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="R35" t="n">
         <v>1.25</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7377,13 +7377,13 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O36" t="n">
         <v>1.34</v>
       </c>
       <c r="P36" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
         <v>1.96</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
         <v>1.04</v>
       </c>
       <c r="N37" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O37" t="n">
         <v>1.24</v>
@@ -7580,7 +7580,7 @@
         <v>2.04</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7604,49 +7604,49 @@
         <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
         <v>17.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
         <v>26</v>
       </c>
       <c r="AG37" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
         <v>23</v>
       </c>
       <c r="AI37" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.38</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.26</v>
+        <v>1.17</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="AU37" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.22</v>
+        <v>1.17</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.18</v>
+        <v>1.12</v>
       </c>
       <c r="AY37" t="n">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.26</v>
+        <v>1.17</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.26</v>
+        <v>1.17</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.28</v>
+        <v>1.17</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.32</v>
+        <v>1.17</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.38</v>
+        <v>1.17</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.38</v>
+        <v>1.17</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>4.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -7941,16 +7941,16 @@
         <v>2.98</v>
       </c>
       <c r="H39" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J39" t="n">
         <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7983,10 +7983,10 @@
         <v>1.98</v>
       </c>
       <c r="V39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.51</v>
       </c>
       <c r="X39" t="n">
         <v>13</v>
@@ -7998,7 +7998,7 @@
         <v>970</v>
       </c>
       <c r="AA39" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB39" t="n">
         <v>970</v>
@@ -8088,17 +8088,17 @@
         <v>1.64</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="BF39" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BG39" t="n">
         <v>8.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G40" t="n">
         <v>2.24</v>
@@ -8141,7 +8141,7 @@
         <v>4.7</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K40" t="n">
         <v>3.3</v>
@@ -8153,7 +8153,7 @@
         <v>1.13</v>
       </c>
       <c r="N40" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O40" t="n">
         <v>1.56</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>2.54</v>
       </c>
       <c r="G41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H41" t="n">
         <v>2.74</v>
@@ -8338,7 +8338,7 @@
         <v>3.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -8526,10 +8526,10 @@
         <v>2.62</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K42" t="n">
         <v>3.95</v>
@@ -8550,7 +8550,7 @@
         <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R42" t="n">
         <v>1.44</v>
@@ -8565,22 +8565,22 @@
         <v>2.16</v>
       </c>
       <c r="V42" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W42" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X42" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="Y42" t="n">
         <v>15.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AA42" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AB42" t="n">
         <v>15</v>
@@ -8592,37 +8592,37 @@
         <v>14.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AF42" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AG42" t="n">
         <v>14.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AI42" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AJ42" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AK42" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AL42" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AM42" t="n">
         <v>85</v>
       </c>
       <c r="AN42" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AO42" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AP42" t="n">
         <v>4.1</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -8720,10 +8720,10 @@
         <v>1.48</v>
       </c>
       <c r="I43" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K43" t="n">
         <v>5.4</v>
@@ -8759,7 +8759,7 @@
         <v>2.04</v>
       </c>
       <c r="V43" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="W43" t="n">
         <v>1.14</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>2.16</v>
       </c>
       <c r="G44" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="H44" t="n">
         <v>3.3</v>
@@ -8917,7 +8917,7 @@
         <v>4.2</v>
       </c>
       <c r="J44" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K44" t="n">
         <v>3.8</v>
@@ -8929,13 +8929,13 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O44" t="n">
         <v>1.34</v>
       </c>
       <c r="P44" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q44" t="n">
         <v>1.96</v>
@@ -8953,10 +8953,10 @@
         <v>1.01</v>
       </c>
       <c r="V44" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W44" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
         <v>2.04</v>
       </c>
       <c r="T45" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U45" t="n">
         <v>2.36</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
         <v>1.7</v>
       </c>
       <c r="U46" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V46" t="n">
         <v>1.25</v>
@@ -9356,7 +9356,7 @@
         <v>40</v>
       </c>
       <c r="AA46" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB46" t="n">
         <v>7.8</v>
@@ -9407,7 +9407,7 @@
         <v>12.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS46" t="n">
         <v>8</v>
@@ -9434,7 +9434,7 @@
         <v>18.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB46" t="n">
         <v>18.5</v>
@@ -9443,7 +9443,7 @@
         <v>19</v>
       </c>
       <c r="BD46" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE46" t="n">
         <v>8</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -9478,179 +9478,179 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Jong Ajax Amsterdam</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="G47" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="H47" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="I47" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K47" t="n">
         <v>4.6</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N47" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="O47" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P47" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="R47" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S47" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V47" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="W47" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -9684,16 +9684,16 @@
         <v>2.46</v>
       </c>
       <c r="G48" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="H48" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I48" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J48" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="K48" t="n">
         <v>4.6</v>
@@ -9714,7 +9714,7 @@
         <v>2.68</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R48" t="n">
         <v>1.58</v>
@@ -9732,7 +9732,7 @@
         <v>1.47</v>
       </c>
       <c r="W48" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,14 +9844,14 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9866,179 +9866,179 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="G49" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="H49" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="I49" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K49" t="n">
         <v>3.95</v>
       </c>
-      <c r="K49" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L49" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M49" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N49" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U49" t="n">
         <v>2.44</v>
       </c>
-      <c r="O49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.42</v>
-      </c>
       <c r="V49" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="W49" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="X49" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y49" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z49" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE49" t="n">
         <v>27</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AF49" t="n">
         <v>23</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AG49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG49" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD49" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -10232,14 +10232,14 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10254,179 +10254,179 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Jong Ajax Amsterdam</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="G51" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="H51" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="J51" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="L51" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N51" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="P51" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="R51" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="S51" t="n">
-        <v>2.68</v>
+        <v>1.99</v>
       </c>
       <c r="T51" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U51" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="W51" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="X51" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y51" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI51" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK51" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL51" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR51" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV51" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW51" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G52" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H52" t="n">
         <v>3.45</v>
@@ -10487,16 +10487,16 @@
         <v>1.14</v>
       </c>
       <c r="P52" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R52" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S52" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T52" t="n">
         <v>1.46</v>
@@ -10505,10 +10505,10 @@
         <v>2.68</v>
       </c>
       <c r="V52" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W52" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X52" t="n">
         <v>38</v>
@@ -10523,7 +10523,7 @@
         <v>75</v>
       </c>
       <c r="AB52" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC52" t="n">
         <v>13.5</v>
@@ -10547,7 +10547,7 @@
         <v>40</v>
       </c>
       <c r="AJ52" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK52" t="n">
         <v>21</v>
@@ -10565,28 +10565,28 @@
         <v>25</v>
       </c>
       <c r="AP52" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AQ52" t="n">
         <v>20</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT52" t="n">
         <v>14</v>
       </c>
       <c r="AU52" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV52" t="n">
         <v>14</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX52" t="n">
         <v>14.5</v>
@@ -10598,7 +10598,7 @@
         <v>12.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB52" t="n">
         <v>20</v>
@@ -10610,7 +10610,7 @@
         <v>20</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BF52" t="n">
         <v>5.9</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G53" t="n">
         <v>2.46</v>
@@ -10687,7 +10687,7 @@
         <v>1.45</v>
       </c>
       <c r="R53" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S53" t="n">
         <v>2.1</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -10854,13 +10854,13 @@
         <v>4.6</v>
       </c>
       <c r="I54" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J54" t="n">
         <v>4.3</v>
       </c>
       <c r="K54" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -10884,13 +10884,13 @@
         <v>1.68</v>
       </c>
       <c r="S54" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T54" t="n">
         <v>1.58</v>
       </c>
       <c r="U54" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V54" t="n">
         <v>1.25</v>
@@ -10950,19 +10950,19 @@
         <v>970</v>
       </c>
       <c r="AO54" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AR54" t="n">
         <v>1.82</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AT54" t="n">
         <v>6</v>
@@ -10971,44 +10971,44 @@
         <v>5.5</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AX54" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY54" t="n">
         <v>5.4</v>
       </c>
       <c r="AZ54" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BA54" t="n">
         <v>1.83</v>
       </c>
       <c r="BB54" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BC54" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BF54" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG54" t="n">
         <v>1.83</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
         <v>24</v>
       </c>
       <c r="AB55" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AC55" t="n">
         <v>17.5</v>
@@ -11120,13 +11120,13 @@
         <v>70</v>
       </c>
       <c r="AG55" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AH55" t="n">
         <v>26</v>
       </c>
       <c r="AI55" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AJ55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -11233,19 +11233,19 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H56" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I56" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J56" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K56" t="n">
         <v>4.6</v>
@@ -11281,10 +11281,10 @@
         <v>1.01</v>
       </c>
       <c r="V56" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W56" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
         <v>2.62</v>
       </c>
       <c r="I57" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J57" t="n">
         <v>3.9</v>
@@ -11475,10 +11475,10 @@
         <v>2.78</v>
       </c>
       <c r="V57" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W57" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X57" t="n">
         <v>34</v>
@@ -11544,7 +11544,7 @@
         <v>20</v>
       </c>
       <c r="AS57" t="n">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT57" t="n">
         <v>15.5</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G58" t="n">
         <v>2.18</v>
@@ -11630,10 +11630,10 @@
         <v>3.45</v>
       </c>
       <c r="I58" t="n">
-        <v>3.95</v>
+        <v>60</v>
       </c>
       <c r="J58" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K58" t="n">
         <v>4</v>
@@ -11645,31 +11645,31 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="O58" t="n">
         <v>1.29</v>
       </c>
       <c r="P58" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="R58" t="n">
         <v>1.27</v>
       </c>
       <c r="S58" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T58" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="U58" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V58" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W58" t="n">
         <v>1.84</v>
@@ -11678,7 +11678,7 @@
         <v>18.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z58" t="n">
         <v>34</v>
@@ -11729,16 +11729,16 @@
         <v>65</v>
       </c>
       <c r="AP58" t="n">
-        <v>3.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ58" t="n">
         <v>11</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AS58" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT58" t="n">
         <v>8.199999999999999</v>
@@ -11750,7 +11750,7 @@
         <v>13</v>
       </c>
       <c r="AW58" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX58" t="n">
         <v>9.6</v>
@@ -11759,19 +11759,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ58" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BA58" t="n">
         <v>4</v>
       </c>
       <c r="BB58" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC58" t="n">
         <v>3.7</v>
       </c>
-      <c r="BC58" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BD58" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE58" t="n">
         <v>4.1</v>
@@ -11780,11 +11780,11 @@
         <v>10</v>
       </c>
       <c r="BG58" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11818,7 @@
         <v>2.08</v>
       </c>
       <c r="G59" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H59" t="n">
         <v>4.2</v>
@@ -11953,10 +11953,10 @@
         <v>10</v>
       </c>
       <c r="AZ59" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA59" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BB59" t="n">
         <v>23</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G60" t="n">
         <v>1.84</v>
@@ -12036,13 +12036,13 @@
         <v>1.81</v>
       </c>
       <c r="O60" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P60" t="n">
         <v>1.81</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R60" t="n">
         <v>1.26</v>
@@ -12051,7 +12051,7 @@
         <v>3.1</v>
       </c>
       <c r="T60" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U60" t="n">
         <v>1.78</v>
@@ -12141,7 +12141,7 @@
         <v>2.92</v>
       </c>
       <c r="AX60" t="n">
-        <v>2.38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY60" t="n">
         <v>2.38</v>
@@ -12153,7 +12153,7 @@
         <v>2.92</v>
       </c>
       <c r="BB60" t="n">
-        <v>2.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC60" t="n">
         <v>2.62</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="G61" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="H61" t="n">
-        <v>2.3</v>
+        <v>1.09</v>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="J61" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K61" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12236,13 +12236,13 @@
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R61" t="n">
         <v>1.12</v>
       </c>
       <c r="S61" t="n">
-        <v>2.74</v>
+        <v>1.28</v>
       </c>
       <c r="T61" t="n">
         <v>1.01</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -12433,10 +12433,10 @@
         <v>1.65</v>
       </c>
       <c r="R62" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="S62" t="n">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="T62" t="n">
         <v>1.01</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G63" t="n">
         <v>2.66</v>
@@ -12609,7 +12609,7 @@
         <v>3.4</v>
       </c>
       <c r="L63" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M63" t="n">
         <v>1.01</v>
@@ -12618,7 +12618,7 @@
         <v>1.7</v>
       </c>
       <c r="O63" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P63" t="n">
         <v>1.7</v>
@@ -12627,16 +12627,16 @@
         <v>2.28</v>
       </c>
       <c r="R63" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S63" t="n">
-        <v>3.85</v>
+        <v>2.28</v>
       </c>
       <c r="T63" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U63" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V63" t="n">
         <v>1.41</v>
@@ -12648,19 +12648,19 @@
         <v>12.5</v>
       </c>
       <c r="Y63" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z63" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA63" t="n">
         <v>75</v>
       </c>
       <c r="AB63" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC63" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD63" t="n">
         <v>970</v>
@@ -12669,10 +12669,10 @@
         <v>50</v>
       </c>
       <c r="AF63" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG63" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH63" t="n">
         <v>22</v>
@@ -12681,7 +12681,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK63" t="n">
         <v>40</v>
@@ -12699,69 +12699,69 @@
         <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="AQ63" t="n">
-        <v>8.800000000000001</v>
+        <v>1.38</v>
       </c>
       <c r="AR63" t="n">
-        <v>15</v>
+        <v>1.38</v>
       </c>
       <c r="AS63" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.92</v>
+        <v>1.38</v>
       </c>
       <c r="AU63" t="n">
-        <v>6.2</v>
+        <v>1.38</v>
       </c>
       <c r="AV63" t="n">
-        <v>10</v>
+        <v>1.28</v>
       </c>
       <c r="AW63" t="n">
-        <v>3.8</v>
+        <v>26</v>
       </c>
       <c r="AX63" t="n">
-        <v>3.35</v>
+        <v>1.38</v>
       </c>
       <c r="AY63" t="n">
-        <v>3.2</v>
+        <v>1.38</v>
       </c>
       <c r="AZ63" t="n">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="BA63" t="n">
-        <v>3.9</v>
+        <v>1.36</v>
       </c>
       <c r="BB63" t="n">
-        <v>3.75</v>
+        <v>1.38</v>
       </c>
       <c r="BC63" t="n">
-        <v>3.7</v>
+        <v>1.34</v>
       </c>
       <c r="BD63" t="n">
-        <v>3.85</v>
+        <v>1.35</v>
       </c>
       <c r="BE63" t="n">
-        <v>4.1</v>
+        <v>1.38</v>
       </c>
       <c r="BF63" t="n">
-        <v>4.1</v>
+        <v>1.38</v>
       </c>
       <c r="BG63" t="n">
-        <v>4.1</v>
+        <v>1.38</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12776,31 +12776,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Morton</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.61</v>
+        <v>4.3</v>
       </c>
       <c r="G64" t="n">
-        <v>1.76</v>
+        <v>5.8</v>
       </c>
       <c r="H64" t="n">
-        <v>5.8</v>
+        <v>1.89</v>
       </c>
       <c r="I64" t="n">
-        <v>7.8</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="K64" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,22 +12809,22 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="O64" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="P64" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R64" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T64" t="n">
         <v>1.01</v>
@@ -12833,10 +12833,10 @@
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.14</v>
+        <v>1.9</v>
       </c>
       <c r="W64" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -12997,13 +12997,13 @@
         <v>3.15</v>
       </c>
       <c r="L65" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M65" t="n">
         <v>1.12</v>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O65" t="n">
         <v>1.47</v>
@@ -13012,7 +13012,7 @@
         <v>1.67</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R65" t="n">
         <v>1.25</v>
@@ -13024,13 +13024,13 @@
         <v>2.02</v>
       </c>
       <c r="U65" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V65" t="n">
         <v>1.32</v>
       </c>
       <c r="W65" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X65" t="n">
         <v>9.4</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -13173,19 +13173,19 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G66" t="n">
-        <v>2.68</v>
+        <v>970</v>
       </c>
       <c r="H66" t="n">
-        <v>3.15</v>
+        <v>1.67</v>
       </c>
       <c r="I66" t="n">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="J66" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="K66" t="n">
         <v>950</v>
@@ -13206,13 +13206,13 @@
         <v>1.65</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R66" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S66" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T66" t="n">
         <v>1.01</v>
@@ -13221,7 +13221,7 @@
         <v>1.01</v>
       </c>
       <c r="V66" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W66" t="n">
         <v>1.59</v>
@@ -13336,14 +13336,14 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13358,179 +13358,179 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Morton</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F67" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H67" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I67" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K67" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W67" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X67" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS67" t="n">
         <v>4.3</v>
       </c>
-      <c r="G67" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I67" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J67" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K67" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S67" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT67" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU67" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV67" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA67" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD67" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG67" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -13552,179 +13552,179 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G68" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H68" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I68" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J68" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K68" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N68" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O68" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="P68" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="R68" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S68" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T68" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="U68" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="V68" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W68" t="n">
         <v>2.3</v>
       </c>
       <c r="X68" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y68" t="n">
         <v>22</v>
       </c>
       <c r="Z68" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA68" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="AB68" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC68" t="n">
         <v>10.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE68" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG68" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH68" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI68" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AJ68" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK68" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL68" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM68" t="n">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="AN68" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO68" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP68" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR68" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS68" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT68" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU68" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW68" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AX68" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY68" t="n">
         <v>9</v>
       </c>
       <c r="AZ68" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA68" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BB68" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC68" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BD68" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE68" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF68" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG68" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -13940,179 +13940,179 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="G70" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="H70" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K70" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
       </c>
       <c r="M70" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>3.35</v>
+        <v>1.62</v>
       </c>
       <c r="O70" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P70" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="R70" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S70" t="n">
         <v>3.2</v>
       </c>
       <c r="T70" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U70" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W70" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X70" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y70" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z70" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA70" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB70" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC70" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD70" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE70" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF70" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG70" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH70" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI70" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ70" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK70" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL70" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM70" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN70" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO70" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP70" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AQ70" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AR70" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS70" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU70" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="AV70" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AW70" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AX70" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY70" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AZ70" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BA70" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB70" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC70" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD70" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE70" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF70" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG70" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -14134,55 +14134,55 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G71" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H71" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K71" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="L71" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>1.01</v>
       </c>
       <c r="N71" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="O71" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="P71" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="R71" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S71" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="T71" t="n">
         <v>1.01</v>
@@ -14191,10 +14191,10 @@
         <v>1.01</v>
       </c>
       <c r="V71" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W71" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X71" t="n">
         <v>1000</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -14328,179 +14328,179 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="G72" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="H72" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S72" t="n">
         <v>3.2</v>
       </c>
-      <c r="K72" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L72" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N72" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O72" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S72" t="n">
-        <v>2.84</v>
-      </c>
       <c r="T72" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U72" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V72" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W72" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="X72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z72" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA72" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC72" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE72" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF72" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG72" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH72" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI72" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ72" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK72" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL72" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM72" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN72" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO72" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT72" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU72" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV72" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW72" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX72" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY72" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ72" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA72" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB72" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC72" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD72" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE72" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF72" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG72" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G73" t="n">
         <v>1.43</v>
@@ -14546,7 +14546,7 @@
         <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14555,7 +14555,7 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O73" t="n">
         <v>1.22</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G74" t="n">
         <v>1.5</v>
@@ -14740,7 +14740,7 @@
         <v>4.9</v>
       </c>
       <c r="K74" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L74" t="n">
         <v>1.33</v>
@@ -14752,7 +14752,7 @@
         <v>4.5</v>
       </c>
       <c r="O74" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P74" t="n">
         <v>2.22</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v>3.95</v>
       </c>
       <c r="H75" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I75" t="n">
         <v>2.82</v>
@@ -14946,7 +14946,7 @@
         <v>1.84</v>
       </c>
       <c r="O75" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P75" t="n">
         <v>1.84</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -15122,13 +15122,13 @@
         <v>1.61</v>
       </c>
       <c r="I76" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="J76" t="n">
         <v>3.8</v>
       </c>
       <c r="K76" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L76" t="n">
         <v>1.01</v>
@@ -15161,7 +15161,7 @@
         <v>1.01</v>
       </c>
       <c r="V76" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="W76" t="n">
         <v>1.14</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -15325,28 +15325,28 @@
         <v>3.65</v>
       </c>
       <c r="L77" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M77" t="n">
         <v>1.08</v>
       </c>
       <c r="N77" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O77" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P77" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R77" t="n">
         <v>1.32</v>
       </c>
       <c r="S77" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T77" t="n">
         <v>1.88</v>
@@ -15412,7 +15412,7 @@
         <v>48</v>
       </c>
       <c r="AO77" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP77" t="n">
         <v>11.5</v>
@@ -15466,18 +15466,18 @@
         <v>40</v>
       </c>
       <c r="BG77" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -15492,31 +15492,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H78" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I78" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J78" t="n">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="K78" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L78" t="n">
         <v>1.01</v>
@@ -15525,22 +15525,22 @@
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="O78" t="n">
         <v>1.01</v>
       </c>
       <c r="P78" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R78" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S78" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="T78" t="n">
         <v>1.01</v>
@@ -15549,10 +15549,10 @@
         <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W78" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -15686,12 +15686,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ES Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -15710,7 +15710,7 @@
         <v>1.02</v>
       </c>
       <c r="K79" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -15719,7 +15719,7 @@
         <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O79" t="n">
         <v>1.01</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -15880,12 +15880,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MC El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Olympique Akbou</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -15913,7 +15913,7 @@
         <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O80" t="n">
         <v>1.01</v>
@@ -15922,13 +15922,13 @@
         <v>1.24</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R80" t="n">
         <v>1.12</v>
       </c>
       <c r="S80" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T80" t="n">
         <v>1.01</v>
@@ -15997,52 +15997,52 @@
         <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF80" t="n">
         <v>1.01</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -16074,12 +16074,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -16098,7 +16098,7 @@
         <v>1.02</v>
       </c>
       <c r="K81" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -16107,7 +16107,7 @@
         <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O81" t="n">
         <v>1.01</v>
@@ -16116,7 +16116,7 @@
         <v>1.24</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R81" t="n">
         <v>1.12</v>
@@ -16246,14 +16246,14 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -16268,31 +16268,31 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>MC El Bayadh</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G82" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="H82" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I82" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J82" t="n">
-        <v>2.72</v>
+        <v>1.02</v>
       </c>
       <c r="K82" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -16301,22 +16301,22 @@
         <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="O82" t="n">
         <v>1.01</v>
       </c>
       <c r="P82" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R82" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S82" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="T82" t="n">
         <v>1.01</v>
@@ -16325,10 +16325,10 @@
         <v>1.01</v>
       </c>
       <c r="V82" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W82" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="X82" t="n">
         <v>1000</v>
@@ -16385,52 +16385,52 @@
         <v>1000</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE82" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF82" t="n">
         <v>1.01</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
@@ -16489,16 +16489,16 @@
         <v>3.3</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P83" t="n">
         <v>1.46</v>
@@ -16507,328 +16507,1104 @@
         <v>2.78</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BG83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-11 19:44:32</t>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH84" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:59:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Wanderers (Uru)</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H85" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W85" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="X85" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:59:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K86" t="n">
+        <v>950</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S86" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH86" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:59:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H87" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I87" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K87" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V87" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W87" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:59:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>Chilean Primera B</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Deportes Iquique</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Cobreloa Calama</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H84" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K84" t="n">
-        <v>950</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH84" t="inlineStr">
-        <is>
-          <t>2026-03-11 19:44:32</t>
+      <c r="F88" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K88" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>2026-03-11 21:59:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.59</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
         <v>1.96</v>
@@ -796,13 +796,13 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.96</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.64</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -957,25 +957,25 @@
         <v>3.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.28</v>
@@ -984,22 +984,22 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
         <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W3" t="n">
         <v>1.45</v>
@@ -1029,7 +1029,7 @@
         <v>980</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
@@ -1056,10 +1056,10 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>11.5</v>
@@ -1089,22 +1089,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
         <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>3.9</v>
@@ -1175,10 +1175,10 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
@@ -1190,10 +1190,10 @@
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W4" t="n">
         <v>1.4</v>
@@ -1259,13 +1259,13 @@
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
@@ -1277,7 +1277,7 @@
         <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
         <v>12.5</v>
@@ -1286,13 +1286,13 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD4" t="n">
         <v>34</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H5" t="n">
         <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="J5" t="n">
         <v>3.15</v>
@@ -1360,13 +1360,13 @@
         <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>1.84</v>
@@ -1375,7 +1375,7 @@
         <v>1.94</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
         <v>3.15</v>
@@ -1387,10 +1387,10 @@
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="G6" t="n">
-        <v>700</v>
+        <v>11.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="I6" t="n">
-        <v>980</v>
+        <v>2.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>2.28</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.42</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.12</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>980</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>980</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="K7" t="n">
-        <v>980</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="O7" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.48</v>
+        <v>2.46</v>
       </c>
       <c r="R7" t="n">
         <v>1.12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
         <v>5.3</v>
@@ -1933,19 +1933,19 @@
         <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
@@ -1963,10 +1963,10 @@
         <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
@@ -2032,25 +2032,25 @@
         <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
         <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.96</v>
+        <v>5.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="AX8" t="n">
         <v>4.4</v>
@@ -2059,32 +2059,32 @@
         <v>4.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.64</v>
+        <v>5.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.9</v>
+        <v>2.94</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.62</v>
+        <v>5.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H9" t="n">
         <v>3.2</v>
@@ -2130,7 +2130,7 @@
         <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.46</v>
@@ -2139,13 +2139,13 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
         <v>2.36</v>
@@ -2154,10 +2154,10 @@
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
         <v>1.83</v>
@@ -2166,7 +2166,7 @@
         <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
@@ -2232,7 +2232,7 @@
         <v>19</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2244,7 +2244,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
         <v>12.5</v>
@@ -2253,32 +2253,32 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2348,19 +2348,19 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2542,13 +2542,13 @@
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2697,40 +2697,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
         <v>1.34</v>
@@ -2748,7 +2748,7 @@
         <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -2906,13 +2906,13 @@
         <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
         <v>3.55</v>
@@ -2924,16 +2924,16 @@
         <v>1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
         <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
         <v>2.12</v>
@@ -2942,13 +2942,13 @@
         <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
         <v>980</v>
@@ -2969,7 +2969,7 @@
         <v>980</v>
       </c>
       <c r="AF13" t="n">
-        <v>980</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
         <v>12</v>
@@ -3008,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT13" t="n">
         <v>9.199999999999999</v>
@@ -3023,38 +3023,38 @@
         <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF13" t="n">
         <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>9.6</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H14" t="n">
         <v>1.4</v>
@@ -3115,22 +3115,22 @@
         <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
         <v>1.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
         <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V14" t="n">
         <v>3.4</v>
@@ -3151,7 +3151,7 @@
         <v>12.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AC14" t="n">
         <v>12.5</v>
@@ -3196,7 +3196,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR14" t="n">
         <v>7.4</v>
@@ -3217,25 +3217,25 @@
         <v>12.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BA14" t="n">
         <v>30</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC14" t="n">
         <v>8.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
         <v>8.4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G15" t="n">
         <v>2.54</v>
@@ -3303,7 +3303,7 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
         <v>1.41</v>
@@ -3315,16 +3315,16 @@
         <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
         <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3333,7 +3333,7 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
         <v>980</v>
@@ -3354,7 +3354,7 @@
         <v>980</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
         <v>980</v>
@@ -3378,7 +3378,7 @@
         <v>60</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
         <v>980</v>
@@ -3390,59 +3390,59 @@
         <v>9.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AU15" t="n">
         <v>3.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AW15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB15" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G16" t="n">
         <v>2.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>2.56</v>
@@ -3497,13 +3497,13 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
         <v>1.55</v>
@@ -3515,16 +3515,16 @@
         <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
         <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
         <v>3.8</v>
@@ -3685,7 +3685,7 @@
         <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -3697,10 +3697,10 @@
         <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R17" t="n">
         <v>1.29</v>
@@ -3718,7 +3718,7 @@
         <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
         <v>1.36</v>
@@ -4079,31 +4079,31 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>1.34</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
         <v>1.87</v>
@@ -4178,7 +4178,7 @@
         <v>1.88</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>1.85</v>
       </c>
       <c r="AV19" t="n">
         <v>2.04</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4285,19 +4285,19 @@
         <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="T20" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W20" t="n">
         <v>1.23</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>3.15</v>
@@ -4464,25 +4464,25 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
         <v>2.88</v>
       </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
         <v>1.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T21" t="n">
         <v>1.87</v>
@@ -4491,10 +4491,10 @@
         <v>1.92</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="X21" t="n">
         <v>980</v>
@@ -4506,7 +4506,7 @@
         <v>980</v>
       </c>
       <c r="AA21" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB21" t="n">
         <v>980</v>
@@ -4530,7 +4530,7 @@
         <v>980</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
         <v>980</v>
@@ -4542,37 +4542,37 @@
         <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
         <v>980</v>
       </c>
       <c r="AO21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="AT21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="AX21" t="n">
         <v>4.9</v>
@@ -4581,32 +4581,32 @@
         <v>4.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="BB21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC21" t="n">
         <v>6</v>
       </c>
-      <c r="BC21" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD21" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="BF21" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>5.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I22" t="n">
         <v>1.82</v>
@@ -4652,7 +4652,7 @@
         <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.3</v>
@@ -4661,7 +4661,7 @@
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.19</v>
@@ -4754,7 +4754,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT22" t="n">
         <v>2.94</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>2.44</v>
       </c>
       <c r="G23" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I23" t="n">
         <v>2.96</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
@@ -4876,13 +4876,13 @@
         <v>1.51</v>
       </c>
       <c r="U23" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V23" t="n">
         <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X23" t="n">
         <v>980</v>
@@ -4894,7 +4894,7 @@
         <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AB23" t="n">
         <v>17.5</v>
@@ -4921,7 +4921,7 @@
         <v>32</v>
       </c>
       <c r="AJ23" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AK23" t="n">
         <v>980</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5031,16 +5031,16 @@
         <v>2.88</v>
       </c>
       <c r="H24" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J24" t="n">
         <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5052,19 +5052,19 @@
         <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
         <v>1.71</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
         <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
         <v>1.84</v>
@@ -5073,7 +5073,7 @@
         <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
         <v>1.53</v>
@@ -5088,7 +5088,7 @@
         <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB24" t="n">
         <v>12</v>
@@ -5169,10 +5169,10 @@
         <v>3.95</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BD24" t="n">
         <v>3.95</v>
@@ -5181,14 +5181,14 @@
         <v>4.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG24" t="n">
         <v>3.85</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G26" t="n">
         <v>2.66</v>
@@ -5443,16 +5443,16 @@
         <v>1.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
         <v>1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
         <v>1.56</v>
@@ -5461,7 +5461,7 @@
         <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W26" t="n">
         <v>1.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5646,10 +5646,10 @@
         <v>1.54</v>
       </c>
       <c r="S27" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
         <v>1.85</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
         <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.32</v>
@@ -5837,7 +5837,7 @@
         <v>1.58</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
         <v>2.44</v>
@@ -5924,7 +5924,7 @@
         <v>2.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.22</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
         <v>2.28</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6213,16 +6213,16 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O30" t="n">
         <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>1.24</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>3.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
@@ -6422,7 +6422,7 @@
         <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G32" t="n">
         <v>2.04</v>
@@ -6592,7 +6592,7 @@
         <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6601,10 +6601,10 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.57</v>
+        <v>2.66</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="P32" t="n">
         <v>1.56</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
         <v>1.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
         <v>1.94</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
         <v>3.35</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
         <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="R35" t="n">
         <v>1.22</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>1.71</v>
       </c>
       <c r="G37" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H37" t="n">
         <v>4.9</v>
@@ -7598,7 +7598,7 @@
         <v>1.21</v>
       </c>
       <c r="W37" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X37" t="n">
         <v>25</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>1.99</v>
       </c>
       <c r="G38" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H38" t="n">
         <v>3.5</v>
@@ -7753,7 +7753,7 @@
         <v>4.6</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K38" t="n">
         <v>3.55</v>
@@ -7792,7 +7792,7 @@
         <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -7944,13 +7944,13 @@
         <v>2.74</v>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,7 +7959,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.99</v>
+        <v>3.75</v>
       </c>
       <c r="O39" t="n">
         <v>1.28</v>
@@ -7968,7 +7968,7 @@
         <v>1.99</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R39" t="n">
         <v>1.13</v>
@@ -7983,10 +7983,10 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W39" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>2.16</v>
       </c>
       <c r="G40" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H40" t="n">
         <v>3.3</v>
@@ -8153,16 +8153,16 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O40" t="n">
         <v>1.34</v>
       </c>
       <c r="P40" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
@@ -8180,7 +8180,7 @@
         <v>1.31</v>
       </c>
       <c r="W40" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G41" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I41" t="n">
         <v>1.6</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8517,13 +8517,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G42" t="n">
         <v>2.94</v>
       </c>
       <c r="H42" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I42" t="n">
         <v>2.96</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G43" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H43" t="n">
         <v>5.7</v>
       </c>
       <c r="I43" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K43" t="n">
         <v>5.8</v>
@@ -8744,7 +8744,7 @@
         <v>2.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R43" t="n">
         <v>1.76</v>
@@ -8753,16 +8753,16 @@
         <v>2.04</v>
       </c>
       <c r="T43" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U43" t="n">
         <v>2.36</v>
       </c>
       <c r="V43" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W43" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X43" t="n">
         <v>48</v>
@@ -8786,7 +8786,7 @@
         <v>34</v>
       </c>
       <c r="AE43" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF43" t="n">
         <v>18</v>
@@ -8810,7 +8810,7 @@
         <v>34</v>
       </c>
       <c r="AM43" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN43" t="n">
         <v>6.6</v>
@@ -8819,13 +8819,13 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ43" t="n">
         <v>2.8</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AS43" t="n">
         <v>2.98</v>
@@ -8846,16 +8846,16 @@
         <v>2.56</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AZ43" t="n">
         <v>2.68</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BB43" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BC43" t="n">
         <v>10</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -8908,13 +8908,13 @@
         <v>2.08</v>
       </c>
       <c r="G44" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H44" t="n">
         <v>4.3</v>
       </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J44" t="n">
         <v>3.15</v>
@@ -8929,7 +8929,7 @@
         <v>1.13</v>
       </c>
       <c r="N44" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O44" t="n">
         <v>1.56</v>
@@ -8947,7 +8947,7 @@
         <v>5.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U44" t="n">
         <v>1.72</v>
@@ -8956,10 +8956,10 @@
         <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y44" t="n">
         <v>11.5</v>
@@ -9007,7 +9007,7 @@
         <v>270</v>
       </c>
       <c r="AN44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO44" t="n">
         <v>160</v>
@@ -9019,10 +9019,10 @@
         <v>10</v>
       </c>
       <c r="AR44" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT44" t="n">
         <v>5.9</v>
@@ -9034,7 +9034,7 @@
         <v>15.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX44" t="n">
         <v>10.5</v>
@@ -9046,29 +9046,29 @@
         <v>21</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB44" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC44" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD44" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9102,10 +9102,10 @@
         <v>2.74</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I45" t="n">
         <v>3.05</v>
@@ -9114,7 +9114,7 @@
         <v>3.1</v>
       </c>
       <c r="K45" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -9210,13 +9210,13 @@
         <v>5.9</v>
       </c>
       <c r="AQ45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR45" t="n">
         <v>6.8</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AT45" t="n">
         <v>5.1</v>
@@ -9228,7 +9228,7 @@
         <v>5.8</v>
       </c>
       <c r="AW45" t="n">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX45" t="n">
         <v>2.78</v>
@@ -9237,32 +9237,32 @@
         <v>5.8</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="BF45" t="n">
-        <v>26</v>
+        <v>1.58</v>
       </c>
       <c r="BG45" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G46" t="n">
         <v>1.68</v>
@@ -9335,7 +9335,7 @@
         <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U46" t="n">
         <v>2</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9684,16 +9684,16 @@
         <v>2.46</v>
       </c>
       <c r="G48" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="H48" t="n">
         <v>2.5</v>
       </c>
       <c r="I48" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J48" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K48" t="n">
         <v>4.6</v>
@@ -9714,13 +9714,13 @@
         <v>2.42</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="R48" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W48" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="G49" t="n">
         <v>3.05</v>
@@ -9884,13 +9884,13 @@
         <v>2.46</v>
       </c>
       <c r="I49" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J49" t="n">
         <v>3.6</v>
       </c>
       <c r="K49" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L49" t="n">
         <v>1.3</v>
@@ -9905,10 +9905,10 @@
         <v>1.22</v>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R49" t="n">
         <v>1.51</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
         <v>4.2</v>
       </c>
       <c r="H50" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I50" t="n">
         <v>2.08</v>
@@ -10084,7 +10084,7 @@
         <v>3.95</v>
       </c>
       <c r="K50" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L50" t="n">
         <v>1.27</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10493,10 +10493,10 @@
         <v>1.43</v>
       </c>
       <c r="R52" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S52" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T52" t="n">
         <v>1.01</v>
@@ -10505,10 +10505,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W52" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         <v>1.88</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H53" t="n">
         <v>3.45</v>
@@ -10684,7 +10684,7 @@
         <v>2.82</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R53" t="n">
         <v>1.74</v>
@@ -10699,10 +10699,10 @@
         <v>2.68</v>
       </c>
       <c r="V53" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W53" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X53" t="n">
         <v>38</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G54" t="n">
         <v>2.48</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11045,13 +11045,13 @@
         <v>1.77</v>
       </c>
       <c r="H55" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I55" t="n">
         <v>5.5</v>
       </c>
       <c r="J55" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K55" t="n">
         <v>5.8</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
         <v>8</v>
       </c>
       <c r="H56" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="I56" t="n">
         <v>1.72</v>
@@ -11248,7 +11248,7 @@
         <v>4.5</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>980</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
         <v>3.85</v>
       </c>
       <c r="I57" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J57" t="n">
         <v>3.95</v>
@@ -11463,10 +11463,10 @@
         <v>1.6</v>
       </c>
       <c r="R57" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>1.6</v>
+        <v>2.48</v>
       </c>
       <c r="T57" t="n">
         <v>1.01</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11621,22 +11621,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G58" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H58" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I58" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J58" t="n">
         <v>3.9</v>
       </c>
       <c r="K58" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11669,10 +11669,10 @@
         <v>2.78</v>
       </c>
       <c r="V58" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W58" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X58" t="n">
         <v>34</v>
@@ -11684,7 +11684,7 @@
         <v>24</v>
       </c>
       <c r="AA58" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB58" t="n">
         <v>18</v>
@@ -11696,7 +11696,7 @@
         <v>14</v>
       </c>
       <c r="AE58" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF58" t="n">
         <v>23</v>
@@ -11726,10 +11726,10 @@
         <v>12.5</v>
       </c>
       <c r="AO58" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AP58" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AQ58" t="n">
         <v>16.5</v>
@@ -11738,7 +11738,7 @@
         <v>20</v>
       </c>
       <c r="AS58" t="n">
-        <v>32</v>
+        <v>5.9</v>
       </c>
       <c r="AT58" t="n">
         <v>15.5</v>
@@ -11762,19 +11762,19 @@
         <v>12.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB58" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BC58" t="n">
         <v>20</v>
       </c>
       <c r="BD58" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BE58" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF58" t="n">
         <v>10.5</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G59" t="n">
         <v>2.18</v>
@@ -11857,7 +11857,7 @@
         <v>2.92</v>
       </c>
       <c r="T59" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U59" t="n">
         <v>1.71</v>
@@ -11923,7 +11923,7 @@
         <v>65</v>
       </c>
       <c r="AP59" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ59" t="n">
         <v>11</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
         <v>3.45</v>
       </c>
       <c r="K60" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L60" t="n">
         <v>1.5</v>
@@ -12042,7 +12042,7 @@
         <v>1.73</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R60" t="n">
         <v>1.27</v>
@@ -12117,7 +12117,7 @@
         <v>80</v>
       </c>
       <c r="AP60" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ60" t="n">
         <v>12</v>
@@ -12168,11 +12168,11 @@
         <v>18</v>
       </c>
       <c r="BG60" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G61" t="n">
         <v>1.82</v>
@@ -12218,7 +12218,7 @@
         <v>3.65</v>
       </c>
       <c r="K61" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12427,10 +12427,10 @@
         <v>1.28</v>
       </c>
       <c r="P62" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R62" t="n">
         <v>1.12</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13021,10 +13021,10 @@
         <v>3.55</v>
       </c>
       <c r="T65" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U65" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V65" t="n">
         <v>1.16</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13197,16 +13197,16 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O66" t="n">
         <v>1.35</v>
       </c>
       <c r="P66" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R66" t="n">
         <v>1.24</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13370,10 +13370,10 @@
         <v>2.32</v>
       </c>
       <c r="G67" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H67" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
         <v>4.1</v>
@@ -13418,7 +13418,7 @@
         <v>1.32</v>
       </c>
       <c r="W67" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X67" t="n">
         <v>9.4</v>
@@ -13445,7 +13445,7 @@
         <v>60</v>
       </c>
       <c r="AF67" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG67" t="n">
         <v>11.5</v>
@@ -13469,16 +13469,16 @@
         <v>140</v>
       </c>
       <c r="AN67" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO67" t="n">
         <v>75</v>
       </c>
       <c r="AP67" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ67" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR67" t="n">
         <v>23</v>
@@ -13514,7 +13514,7 @@
         <v>27</v>
       </c>
       <c r="BC67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD67" t="n">
         <v>44</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13564,19 +13564,19 @@
         <v>2.2</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52</v>
+        <v>110</v>
       </c>
       <c r="H68" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
         <v>4.4</v>
       </c>
       <c r="J68" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="K68" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
@@ -13585,10 +13585,10 @@
         <v>1.01</v>
       </c>
       <c r="N68" t="n">
-        <v>1.65</v>
+        <v>2.96</v>
       </c>
       <c r="O68" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="P68" t="n">
         <v>1.65</v>
@@ -13609,10 +13609,10 @@
         <v>1.01</v>
       </c>
       <c r="V68" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W68" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="X68" t="n">
         <v>1000</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13755,10 +13755,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G69" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H69" t="n">
         <v>6.2</v>
@@ -13770,7 +13770,7 @@
         <v>3.6</v>
       </c>
       <c r="K69" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -13806,7 +13806,7 @@
         <v>1.15</v>
       </c>
       <c r="W69" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X69" t="n">
         <v>14</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="G70" t="n">
         <v>2.12</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14167,16 +14167,16 @@
         <v>1.01</v>
       </c>
       <c r="N71" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="O71" t="n">
         <v>1.25</v>
       </c>
       <c r="P71" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="R71" t="n">
         <v>1.2</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14346,7 @@
         <v>3.05</v>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>2.92</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
         <v>2.82</v>
       </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>3.2</v>
@@ -14555,16 +14555,16 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="O73" t="n">
         <v>1.29</v>
       </c>
       <c r="P73" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="R73" t="n">
         <v>1.29</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -14749,13 +14749,13 @@
         <v>1.07</v>
       </c>
       <c r="N74" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O74" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P74" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Q74" t="n">
         <v>1.84</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
         <v>17</v>
       </c>
       <c r="AQ76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR76" t="n">
         <v>10.5</v>
@@ -15236,13 +15236,13 @@
         <v>8</v>
       </c>
       <c r="AU76" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW76" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX76" t="n">
         <v>8.199999999999999</v>
@@ -15254,7 +15254,7 @@
         <v>20</v>
       </c>
       <c r="BA76" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="BB76" t="n">
         <v>11.5</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -15316,13 +15316,13 @@
         <v>1.61</v>
       </c>
       <c r="I77" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="J77" t="n">
         <v>3.85</v>
       </c>
       <c r="K77" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
@@ -15340,7 +15340,7 @@
         <v>1.87</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="R77" t="n">
         <v>1.29</v>
@@ -15355,7 +15355,7 @@
         <v>1.01</v>
       </c>
       <c r="V77" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="W77" t="n">
         <v>1.14</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15606,7 @@
         <v>48</v>
       </c>
       <c r="AO78" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP78" t="n">
         <v>11.5</v>
@@ -15651,7 +15651,7 @@
         <v>40</v>
       </c>
       <c r="BD78" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE78" t="n">
         <v>40</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15713,7 @@
         <v>5.9</v>
       </c>
       <c r="L79" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M79" t="n">
         <v>1.01</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -15889,46 +15889,46 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="G80" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="H80" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I80" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J80" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="K80" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L80" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M80" t="n">
         <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="O80" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P80" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="R80" t="n">
         <v>1.12</v>
       </c>
       <c r="S80" t="n">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="T80" t="n">
         <v>1.01</v>
@@ -15937,10 +15937,10 @@
         <v>1.01</v>
       </c>
       <c r="V80" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W80" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X80" t="n">
         <v>1000</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16083,46 +16083,46 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G81" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H81" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I81" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J81" t="n">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="K81" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L81" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M81" t="n">
         <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="O81" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P81" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="R81" t="n">
         <v>1.12</v>
       </c>
       <c r="S81" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="T81" t="n">
         <v>1.01</v>
@@ -16131,10 +16131,10 @@
         <v>1.01</v>
       </c>
       <c r="V81" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W81" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16277,46 +16277,46 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G82" t="n">
-        <v>1000</v>
+        <v>1.64</v>
       </c>
       <c r="H82" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="I82" t="n">
         <v>1000</v>
       </c>
       <c r="J82" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K82" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L82" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M82" t="n">
         <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="O82" t="n">
         <v>1.02</v>
       </c>
       <c r="P82" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="R82" t="n">
         <v>1.12</v>
       </c>
       <c r="S82" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="T82" t="n">
         <v>1.01</v>
@@ -16328,7 +16328,7 @@
         <v>1.01</v>
       </c>
       <c r="W82" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="X82" t="n">
         <v>1000</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16471,46 +16471,46 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="G83" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H83" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I83" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J83" t="n">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="K83" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L83" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M83" t="n">
         <v>1.01</v>
       </c>
       <c r="N83" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O83" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P83" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="R83" t="n">
         <v>1.12</v>
       </c>
       <c r="S83" t="n">
-        <v>1.56</v>
+        <v>2.58</v>
       </c>
       <c r="T83" t="n">
         <v>1.01</v>
@@ -16519,10 +16519,10 @@
         <v>1.01</v>
       </c>
       <c r="V83" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W83" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X83" t="n">
         <v>1000</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -16683,7 +16683,7 @@
         <v>3.3</v>
       </c>
       <c r="L84" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M84" t="n">
         <v>1.13</v>
@@ -16692,7 +16692,7 @@
         <v>1.46</v>
       </c>
       <c r="O84" t="n">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="P84" t="n">
         <v>1.46</v>
@@ -16719,7 +16719,7 @@
         <v>1.83</v>
       </c>
       <c r="X84" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y84" t="n">
         <v>14.5</v>
@@ -16776,59 +16776,59 @@
         <v>2.58</v>
       </c>
       <c r="AQ84" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AR84" t="n">
         <v>22</v>
       </c>
       <c r="AS84" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="AT84" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB84" t="n">
         <v>2.4</v>
       </c>
-      <c r="AU84" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV84" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW84" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB84" t="n">
-        <v>20</v>
-      </c>
       <c r="BC84" t="n">
-        <v>22</v>
+        <v>2.4</v>
       </c>
       <c r="BD84" t="n">
-        <v>3.3</v>
+        <v>46</v>
       </c>
       <c r="BE84" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="BF84" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="BG84" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17077,19 +17077,19 @@
         <v>1.01</v>
       </c>
       <c r="N86" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="O86" t="n">
         <v>1.31</v>
       </c>
       <c r="P86" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="Q86" t="n">
         <v>1.98</v>
       </c>
       <c r="R86" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="S86" t="n">
         <v>3.1</v>
@@ -17131,7 +17131,7 @@
         <v>1000</v>
       </c>
       <c r="AF86" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AG86" t="n">
         <v>970</v>
@@ -17161,62 +17161,62 @@
         <v>1000</v>
       </c>
       <c r="AP86" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AQ86" t="n">
         <v>3.05</v>
       </c>
-      <c r="AQ86" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AR86" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AS86" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AU86" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="AV86" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AW86" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AX86" t="n">
         <v>2.66</v>
       </c>
       <c r="AY86" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="AZ86" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BA86" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BB86" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="BC86" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="BD86" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE86" t="n">
         <v>3.4</v>
-      </c>
-      <c r="BE86" t="n">
-        <v>3.65</v>
       </c>
       <c r="BF86" t="n">
         <v>5.8</v>
       </c>
       <c r="BG86" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17247,25 +17247,25 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="G87" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="H87" t="n">
         <v>4</v>
       </c>
       <c r="I87" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J87" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K87" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="L87" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M87" t="n">
         <v>1.01</v>
@@ -17274,7 +17274,7 @@
         <v>1.51</v>
       </c>
       <c r="O87" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P87" t="n">
         <v>1.51</v>
@@ -17295,10 +17295,10 @@
         <v>1.01</v>
       </c>
       <c r="V87" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W87" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X87" t="n">
         <v>1000</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G88" t="n">
         <v>1.96</v>
@@ -17453,10 +17453,10 @@
         <v>5.2</v>
       </c>
       <c r="J88" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K88" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L88" t="n">
         <v>1.01</v>
@@ -17465,7 +17465,7 @@
         <v>1.08</v>
       </c>
       <c r="N88" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O88" t="n">
         <v>1.37</v>
@@ -17477,16 +17477,16 @@
         <v>2.06</v>
       </c>
       <c r="R88" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S88" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T88" t="n">
         <v>1.89</v>
       </c>
       <c r="U88" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V88" t="n">
         <v>1.25</v>
@@ -17540,7 +17540,7 @@
         <v>44</v>
       </c>
       <c r="AM88" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN88" t="n">
         <v>970</v>
@@ -17555,7 +17555,7 @@
         <v>5.6</v>
       </c>
       <c r="AR88" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS88" t="n">
         <v>1.98</v>
@@ -17567,7 +17567,7 @@
         <v>6.8</v>
       </c>
       <c r="AV88" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW88" t="n">
         <v>7.8</v>
@@ -17582,7 +17582,7 @@
         <v>6.2</v>
       </c>
       <c r="BA88" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB88" t="n">
         <v>6.2</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17638,22 +17638,22 @@
         <v>2.2</v>
       </c>
       <c r="G89" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="H89" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J89" t="n">
         <v>2.88</v>
       </c>
       <c r="K89" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="L89" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M89" t="n">
         <v>1.01</v>
@@ -17683,10 +17683,10 @@
         <v>1.01</v>
       </c>
       <c r="V89" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W89" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X89" t="n">
         <v>1000</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
         <v>1.64</v>
       </c>
       <c r="G90" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H90" t="n">
         <v>6.6</v>
@@ -17844,7 +17844,7 @@
         <v>3.45</v>
       </c>
       <c r="K90" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G91" t="n">
         <v>2.36</v>
@@ -18038,7 +18038,7 @@
         <v>3.5</v>
       </c>
       <c r="K91" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L91" t="n">
         <v>1.01</v>
@@ -18047,13 +18047,13 @@
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O91" t="n">
         <v>1.28</v>
       </c>
       <c r="P91" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q91" t="n">
         <v>1.88</v>
@@ -18131,7 +18131,7 @@
         <v>1000</v>
       </c>
       <c r="AP91" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="AQ91" t="n">
         <v>10.5</v>
@@ -18149,7 +18149,7 @@
         <v>7</v>
       </c>
       <c r="AV91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW91" t="n">
         <v>30</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18223,16 +18223,16 @@
         <v>1.42</v>
       </c>
       <c r="H92" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I92" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="K92" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -18241,34 +18241,34 @@
         <v>1.05</v>
       </c>
       <c r="N92" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O92" t="n">
         <v>1.29</v>
       </c>
       <c r="P92" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R92" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T92" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U92" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="V92" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W92" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -18289,7 +18289,7 @@
         <v>16</v>
       </c>
       <c r="AD92" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE92" t="n">
         <v>1000</v>
@@ -18298,10 +18298,10 @@
         <v>9.6</v>
       </c>
       <c r="AG92" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH92" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI92" t="n">
         <v>1000</v>
@@ -18313,74 +18313,74 @@
         <v>23</v>
       </c>
       <c r="AL92" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM92" t="n">
         <v>1000</v>
       </c>
       <c r="AN92" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO92" t="n">
         <v>1000</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AQ92" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="AR92" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AS92" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AT92" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="AU92" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AV92" t="n">
-        <v>2.04</v>
+        <v>2.68</v>
       </c>
       <c r="AW92" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AX92" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="AY92" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AZ92" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="BA92" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="BB92" t="n">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="BC92" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="BD92" t="n">
-        <v>2.04</v>
+        <v>2.68</v>
       </c>
       <c r="BE92" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="BF92" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG92" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-12 00:17:21</t>
+          <t>2026-03-12 02:35:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-13.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
         <v>4.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I2" t="n">
         <v>2.48</v>
@@ -799,16 +799,16 @@
         <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -817,7 +817,7 @@
         <v>9.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
         <v>34</v>
@@ -829,7 +829,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>30</v>
@@ -844,7 +844,7 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>100</v>
@@ -853,7 +853,7 @@
         <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>25</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AZ2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="BC2" t="n">
         <v>5</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J3" t="n">
         <v>3.65</v>
@@ -969,7 +969,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -981,28 +981,28 @@
         <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
         <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
         <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
         <v>2.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
         <v>17</v>
@@ -1011,10 +1011,10 @@
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB3" t="n">
         <v>14</v>
@@ -1023,7 +1023,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
         <v>28</v>
@@ -1038,22 +1038,22 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
         <v>18.5</v>
@@ -1062,13 +1062,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -1083,28 +1083,28 @@
         <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE3" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
         <v>21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
         <v>2.26</v>
@@ -1175,13 +1175,13 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
         <v>3.1</v>
@@ -1190,13 +1190,13 @@
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
         <v>19.5</v>
@@ -1211,16 +1211,16 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF4" t="n">
         <v>26</v>
@@ -1244,7 +1244,7 @@
         <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
         <v>32</v>
@@ -1289,26 +1289,26 @@
         <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
         <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>3.15</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
         <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1387,10 +1387,10 @@
         <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1411,7 +1411,7 @@
         <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1450,31 +1450,31 @@
         <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
         <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>12.5</v>
@@ -1483,26 +1483,26 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="I6" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
@@ -1560,19 +1560,19 @@
         <v>2.08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P6" t="n">
         <v>1.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1581,10 +1581,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
         <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>2.5</v>
@@ -1754,13 +1754,13 @@
         <v>2.26</v>
       </c>
       <c r="O7" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.15</v>
@@ -1769,16 +1769,16 @@
         <v>5.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
         <v>1.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
         <v>8.4</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
         <v>8.199999999999999</v>
@@ -1838,59 +1838,59 @@
         <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G8" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
@@ -1939,7 +1939,7 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1951,13 +1951,13 @@
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
         <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
         <v>3.9</v>
@@ -1972,7 +1972,7 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
         <v>980</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ8" t="n">
         <v>6.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H9" t="n">
         <v>3.2</v>
@@ -2145,16 +2145,16 @@
         <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
         <v>1.98</v>
@@ -2208,7 +2208,7 @@
         <v>44</v>
       </c>
       <c r="AK9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2226,10 +2226,10 @@
         <v>8.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS9" t="n">
         <v>5</v>
@@ -2253,7 +2253,7 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18.5</v>
+        <v>4.8</v>
       </c>
       <c r="BA9" t="n">
         <v>5</v>
@@ -2271,14 +2271,14 @@
         <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
         <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="G10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2348,7 +2348,7 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2360,7 +2360,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>2.74</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
         <v>4.3</v>
@@ -2542,7 +2542,7 @@
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="T11" t="n">
         <v>2.08</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G12" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>7.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.3</v>
@@ -2721,7 +2721,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.28</v>
@@ -2730,7 +2730,7 @@
         <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.39</v>
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
         <v>1.96</v>
@@ -2748,7 +2748,7 @@
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2799,7 +2799,7 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -2808,59 +2808,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.52</v>
+        <v>4.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BF12" t="n">
         <v>6.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>2.52</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I13" t="n">
         <v>3.15</v>
@@ -2912,10 +2912,10 @@
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
         <v>1.35</v>
@@ -2933,22 +2933,22 @@
         <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
         <v>980</v>
@@ -2960,13 +2960,13 @@
         <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
         <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
         <v>16.5</v>
@@ -2975,7 +2975,7 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
         <v>980</v>
@@ -2993,7 +2993,7 @@
         <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>980</v>
@@ -3002,28 +3002,28 @@
         <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
@@ -3032,29 +3032,29 @@
         <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BD13" t="n">
         <v>10.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K14" t="n">
         <v>5.3</v>
@@ -3118,43 +3118,43 @@
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R14" t="n">
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AA14" t="n">
         <v>12.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
@@ -3163,7 +3163,7 @@
         <v>980</v>
       </c>
       <c r="AF14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AG14" t="n">
         <v>980</v>
@@ -3175,28 +3175,28 @@
         <v>980</v>
       </c>
       <c r="AJ14" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AK14" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AL14" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM14" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN14" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AO14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR14" t="n">
         <v>7.4</v>
@@ -3205,10 +3205,10 @@
         <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV14" t="n">
         <v>8.800000000000001</v>
@@ -3217,38 +3217,38 @@
         <v>12.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA14" t="n">
         <v>30</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3303,10 +3303,10 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
         <v>1.68</v>
@@ -3318,7 +3318,7 @@
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
         <v>1.88</v>
@@ -3345,10 +3345,10 @@
         <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>980</v>
       </c>
       <c r="AD15" t="n">
         <v>980</v>
@@ -3390,13 +3390,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="AT15" t="n">
         <v>4.3</v>
@@ -3405,44 +3405,44 @@
         <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.35</v>
+        <v>2.38</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="BC15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF15" t="n">
         <v>6</v>
       </c>
-      <c r="BD15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.22</v>
+        <v>1.09</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3497,34 +3497,34 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O16" t="n">
         <v>1.19</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R16" t="n">
         <v>1.42</v>
       </c>
       <c r="S16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.34</v>
       </c>
-      <c r="T16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.32</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
         <v>3.8</v>
@@ -3691,7 +3691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>1.3</v>
@@ -3700,7 +3700,7 @@
         <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R17" t="n">
         <v>1.35</v>
@@ -3715,7 +3715,7 @@
         <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.84</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
         <v>3.65</v>
@@ -4079,34 +4079,34 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.27</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.24</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4127,7 +4127,7 @@
         <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
         <v>80</v>
@@ -4139,86 +4139,86 @@
         <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW19" t="n">
         <v>2.46</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AX19" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="BF19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4267,16 +4267,16 @@
         <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
         <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
         <v>2.22</v>
@@ -4306,7 +4306,7 @@
         <v>24</v>
       </c>
       <c r="Y20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
         <v>13.5</v>
@@ -4390,29 +4390,29 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE20" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE20" t="n">
+      <c r="BF20" t="n">
         <v>5</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>4.9</v>
       </c>
       <c r="BG20" t="n">
         <v>6.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>5.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I22" t="n">
         <v>1.8</v>
@@ -4673,7 +4673,7 @@
         <v>1.64</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
         <v>2.4</v>
@@ -4688,7 +4688,7 @@
         <v>2.24</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
         <v>24</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G23" t="n">
         <v>2.62</v>
       </c>
       <c r="H23" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I23" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.26</v>
@@ -4855,13 +4855,13 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O23" t="n">
         <v>1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
         <v>1.55</v>
@@ -4879,7 +4879,7 @@
         <v>2.72</v>
       </c>
       <c r="V23" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W23" t="n">
         <v>1.61</v>
@@ -4888,7 +4888,7 @@
         <v>980</v>
       </c>
       <c r="Y23" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z23" t="n">
         <v>23</v>
@@ -4930,37 +4930,37 @@
         <v>980</v>
       </c>
       <c r="AM23" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AN23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
         <v>17</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR23" t="n">
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX23" t="n">
         <v>18.5</v>
@@ -4975,16 +4975,16 @@
         <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC23" t="n">
         <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF23" t="n">
         <v>10</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
         <v>3.3</v>
@@ -5055,7 +5055,7 @@
         <v>1.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -5064,7 +5064,7 @@
         <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
         <v>1.84</v>
@@ -5130,7 +5130,7 @@
         <v>40</v>
       </c>
       <c r="AO24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
@@ -5166,13 +5166,13 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB24" t="n">
         <v>3.95</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BD24" t="n">
         <v>3.95</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5237,13 +5237,13 @@
         <v>5.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="O25" t="n">
         <v>1.2</v>
@@ -5258,13 +5258,13 @@
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
         <v>1.53</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G26" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H26" t="n">
         <v>2.74</v>
       </c>
       <c r="I26" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J26" t="n">
         <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M26" t="n">
         <v>1.04</v>
@@ -5443,28 +5443,28 @@
         <v>1.19</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R26" t="n">
         <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
         <v>1.56</v>
       </c>
       <c r="U26" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
         <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5482,7 +5482,7 @@
         <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
         <v>1000</v>
@@ -5530,10 +5530,10 @@
         <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
         <v>3.45</v>
@@ -5545,13 +5545,13 @@
         <v>4.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BA26" t="n">
         <v>4.5</v>
@@ -5563,20 +5563,20 @@
         <v>4.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF26" t="n">
         <v>3.95</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>1.32</v>
       </c>
       <c r="G27" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H27" t="n">
         <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
         <v>5.4</v>
@@ -5643,22 +5643,22 @@
         <v>1.62</v>
       </c>
       <c r="R27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U27" t="n">
         <v>1.85</v>
       </c>
       <c r="V27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="X27" t="n">
         <v>25</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I28" t="n">
         <v>2.2</v>
@@ -5834,13 +5834,13 @@
         <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="R28" t="n">
         <v>1.49</v>
       </c>
       <c r="S28" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
@@ -5852,7 +5852,7 @@
         <v>1.83</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
         <v>22</v>
@@ -5918,7 +5918,7 @@
         <v>12.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT28" t="n">
         <v>14.5</v>
@@ -5933,7 +5933,7 @@
         <v>17.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5942,7 +5942,7 @@
         <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
         <v>7.6</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>2.7</v>
       </c>
       <c r="G29" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H29" t="n">
         <v>2.62</v>
@@ -6010,7 +6010,7 @@
         <v>3.8</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6022,7 +6022,7 @@
         <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
         <v>2.04</v>
@@ -6049,7 +6049,7 @@
         <v>1.55</v>
       </c>
       <c r="X29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
         <v>13</v>
@@ -6064,7 +6064,7 @@
         <v>13.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
         <v>12.5</v>
@@ -6094,7 +6094,7 @@
         <v>40</v>
       </c>
       <c r="AM29" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="n">
         <v>28</v>
@@ -6112,7 +6112,7 @@
         <v>15</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT29" t="n">
         <v>11</v>
@@ -6124,7 +6124,7 @@
         <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX29" t="n">
         <v>17</v>
@@ -6136,19 +6136,19 @@
         <v>14</v>
       </c>
       <c r="BA29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC29" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB29" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF29" t="n">
         <v>17</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G30" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="H30" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6213,10 +6213,10 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.61</v>
+        <v>2.58</v>
       </c>
       <c r="O30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P30" t="n">
         <v>1.61</v>
@@ -6231,16 +6231,16 @@
         <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W30" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>1.97</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
         <v>7.2</v>
@@ -6401,7 +6401,7 @@
         <v>3.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
@@ -6410,25 +6410,25 @@
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P31" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
         <v>1.16</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
         <v>2.16</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="P32" t="n">
         <v>1.56</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>1.58</v>
       </c>
       <c r="H33" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I33" t="n">
         <v>11.5</v>
@@ -6786,7 +6786,7 @@
         <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,16 +6795,16 @@
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P33" t="n">
         <v>1.73</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R33" t="n">
         <v>1.27</v>
@@ -6813,7 +6813,7 @@
         <v>3.9</v>
       </c>
       <c r="T33" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U33" t="n">
         <v>1.66</v>
@@ -6822,10 +6822,10 @@
         <v>1.11</v>
       </c>
       <c r="W33" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
         <v>1000</v>
@@ -6837,7 +6837,7 @@
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC33" t="n">
         <v>12</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT33" t="n">
         <v>5.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AV33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>4</v>
       </c>
-      <c r="AW33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BA33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BC33" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7007,10 +7007,10 @@
         <v>3.35</v>
       </c>
       <c r="T34" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
         <v>1.19</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>1.53</v>
       </c>
       <c r="G35" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H35" t="n">
         <v>7</v>
@@ -7174,7 +7174,7 @@
         <v>3.85</v>
       </c>
       <c r="K35" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L35" t="n">
         <v>1.43</v>
@@ -7183,16 +7183,16 @@
         <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
         <v>1.37</v>
       </c>
       <c r="P35" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="R35" t="n">
         <v>1.28</v>
@@ -7201,16 +7201,16 @@
         <v>3.85</v>
       </c>
       <c r="T35" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V35" t="n">
         <v>1.11</v>
       </c>
       <c r="W35" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X35" t="n">
         <v>15.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G36" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>3.1</v>
       </c>
       <c r="K36" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="L36" t="n">
         <v>1.38</v>
@@ -7380,13 +7380,13 @@
         <v>2.42</v>
       </c>
       <c r="O36" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="P36" t="n">
         <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="R36" t="n">
         <v>1.2</v>
@@ -7401,10 +7401,10 @@
         <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W36" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G37" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J37" t="n">
         <v>3.95</v>
       </c>
       <c r="K37" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7577,10 +7577,10 @@
         <v>1.24</v>
       </c>
       <c r="P37" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R37" t="n">
         <v>1.4</v>
@@ -7592,13 +7592,13 @@
         <v>1.64</v>
       </c>
       <c r="U37" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W37" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X37" t="n">
         <v>25</v>
@@ -7625,7 +7625,7 @@
         <v>90</v>
       </c>
       <c r="AF37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG37" t="n">
         <v>15</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AT37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU37" t="n">
         <v>2.24</v>
       </c>
-      <c r="AU37" t="n">
-        <v>2.22</v>
-      </c>
       <c r="AV37" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AX37" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY37" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ37" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BB37" t="n">
         <v>2.44</v>
       </c>
-      <c r="BA37" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>2.42</v>
-      </c>
       <c r="BC37" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BF37" t="n">
         <v>6.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="G38" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="H38" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I38" t="n">
         <v>4.4</v>
@@ -7762,37 +7762,37 @@
         <v>1.39</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
         <v>1.63</v>
       </c>
       <c r="O38" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S38" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T38" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U38" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W38" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -7938,10 +7938,10 @@
         <v>2.62</v>
       </c>
       <c r="G39" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="H39" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I39" t="n">
         <v>3</v>
@@ -7950,10 +7950,10 @@
         <v>3.35</v>
       </c>
       <c r="K39" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L39" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
         <v>1.06</v>
@@ -7986,7 +7986,7 @@
         <v>1.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8001,7 +8001,7 @@
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC39" t="n">
         <v>1000</v>
@@ -8034,7 +8034,7 @@
         <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AR39" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS39" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW39" t="n">
         <v>3.5</v>
       </c>
-      <c r="AT39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV39" t="n">
+      <c r="AX39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY39" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AZ39" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BB39" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BC39" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BD39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG39" t="n">
         <v>5.9</v>
       </c>
-      <c r="BE39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G40" t="n">
         <v>2.44</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="J40" t="n">
         <v>3.35</v>
       </c>
       <c r="K40" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8153,7 +8153,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.87</v>
+        <v>2.78</v>
       </c>
       <c r="O40" t="n">
         <v>1.34</v>
@@ -8162,7 +8162,7 @@
         <v>1.87</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
@@ -8171,13 +8171,13 @@
         <v>2.92</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W40" t="n">
         <v>1.69</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -8326,19 +8326,19 @@
         <v>6.2</v>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H41" t="n">
         <v>1.5</v>
       </c>
       <c r="I41" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J41" t="n">
         <v>4.6</v>
       </c>
       <c r="K41" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8347,16 +8347,16 @@
         <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O41" t="n">
         <v>1.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R41" t="n">
         <v>1.53</v>
@@ -8365,7 +8365,7 @@
         <v>2.52</v>
       </c>
       <c r="T41" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="U41" t="n">
         <v>2.06</v>
@@ -8482,11 +8482,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G42" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H42" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I42" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J42" t="n">
         <v>3.25</v>
@@ -8550,7 +8550,7 @@
         <v>2.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R42" t="n">
         <v>1.44</v>
@@ -8559,13 +8559,13 @@
         <v>2.92</v>
       </c>
       <c r="T42" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="U42" t="n">
         <v>2.18</v>
       </c>
       <c r="V42" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W42" t="n">
         <v>1.53</v>
@@ -8574,10 +8574,10 @@
         <v>21</v>
       </c>
       <c r="Y42" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="Z42" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AA42" t="n">
         <v>980</v>
@@ -8586,7 +8586,7 @@
         <v>980</v>
       </c>
       <c r="AC42" t="n">
-        <v>10</v>
+        <v>980</v>
       </c>
       <c r="AD42" t="n">
         <v>14.5</v>
@@ -8598,7 +8598,7 @@
         <v>980</v>
       </c>
       <c r="AG42" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="AH42" t="n">
         <v>980</v>
@@ -8625,62 +8625,62 @@
         <v>980</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS42" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT42" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AV42" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AW42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BA42" t="n">
-        <v>26</v>
+        <v>6.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BF42" t="n">
         <v>15</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G43" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H43" t="n">
         <v>5.5</v>
@@ -8726,7 +8726,7 @@
         <v>4.7</v>
       </c>
       <c r="K43" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
         <v>1.13</v>
       </c>
       <c r="N44" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O44" t="n">
         <v>1.58</v>
@@ -8950,7 +8950,7 @@
         <v>2.24</v>
       </c>
       <c r="U44" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V44" t="n">
         <v>1.27</v>
@@ -9043,7 +9043,7 @@
         <v>10</v>
       </c>
       <c r="AZ44" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA44" t="n">
         <v>11</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -9099,19 +9099,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="H45" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="I45" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="J45" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K45" t="n">
         <v>3.4</v>
@@ -9123,19 +9123,19 @@
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O45" t="n">
         <v>1.41</v>
       </c>
       <c r="P45" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R45" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S45" t="n">
         <v>4.1</v>
@@ -9147,10 +9147,10 @@
         <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W45" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X45" t="n">
         <v>13.5</v>
@@ -9165,7 +9165,7 @@
         <v>980</v>
       </c>
       <c r="AB45" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="AC45" t="n">
         <v>980</v>
@@ -9180,7 +9180,7 @@
         <v>980</v>
       </c>
       <c r="AG45" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AH45" t="n">
         <v>980</v>
@@ -9198,71 +9198,71 @@
         <v>55</v>
       </c>
       <c r="AM45" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN45" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO45" t="n">
         <v>980</v>
       </c>
       <c r="AP45" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ45" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AR45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE45" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY45" t="n">
+      <c r="BF45" t="n">
         <v>6</v>
       </c>
-      <c r="AZ45" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BG45" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G46" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H46" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I46" t="n">
         <v>7</v>
@@ -9311,7 +9311,7 @@
         <v>4.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M46" t="n">
         <v>1.05</v>
@@ -9323,28 +9323,28 @@
         <v>1.26</v>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q46" t="n">
         <v>1.74</v>
       </c>
       <c r="R46" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
         <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U46" t="n">
         <v>2.02</v>
       </c>
       <c r="V46" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W46" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X46" t="n">
         <v>23</v>
@@ -9371,7 +9371,7 @@
         <v>110</v>
       </c>
       <c r="AF46" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG46" t="n">
         <v>10.5</v>
@@ -9407,10 +9407,10 @@
         <v>19</v>
       </c>
       <c r="AR46" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT46" t="n">
         <v>8</v>
@@ -9422,7 +9422,7 @@
         <v>20</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX46" t="n">
         <v>8.800000000000001</v>
@@ -9434,7 +9434,7 @@
         <v>18</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB46" t="n">
         <v>13</v>
@@ -9443,7 +9443,7 @@
         <v>14</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE46" t="n">
         <v>6</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -9490,22 +9490,22 @@
         <v>1.91</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I47" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J47" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K47" t="n">
         <v>3.8</v>
       </c>
       <c r="L47" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
@@ -9538,7 +9538,7 @@
         <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X47" t="n">
         <v>13.5</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -9681,19 +9681,19 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G48" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="H48" t="n">
         <v>2.5</v>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J48" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K48" t="n">
         <v>4.6</v>
@@ -9705,16 +9705,16 @@
         <v>1.02</v>
       </c>
       <c r="N48" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O48" t="n">
         <v>1.13</v>
       </c>
       <c r="P48" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="R48" t="n">
         <v>1.62</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W48" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -9875,58 +9875,58 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G49" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H49" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I49" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J49" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K49" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L49" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
       </c>
       <c r="N49" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O49" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R49" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S49" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T49" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U49" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V49" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W49" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X49" t="n">
         <v>23</v>
@@ -9968,7 +9968,7 @@
         <v>980</v>
       </c>
       <c r="AK49" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AL49" t="n">
         <v>980</v>
@@ -9983,52 +9983,52 @@
         <v>980</v>
       </c>
       <c r="AP49" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ49" t="n">
         <v>12</v>
       </c>
       <c r="AR49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS49" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT49" t="n">
         <v>12.5</v>
       </c>
       <c r="AU49" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AV49" t="n">
         <v>10.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AX49" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AY49" t="n">
         <v>11</v>
       </c>
       <c r="AZ49" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BA49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB49" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC49" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BD49" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE49" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF49" t="n">
         <v>15</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -10072,13 +10072,13 @@
         <v>3.55</v>
       </c>
       <c r="G50" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H50" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J50" t="n">
         <v>3.95</v>
@@ -10093,7 +10093,7 @@
         <v>1.03</v>
       </c>
       <c r="N50" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O50" t="n">
         <v>1.19</v>
@@ -10117,10 +10117,10 @@
         <v>2.42</v>
       </c>
       <c r="V50" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W50" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X50" t="n">
         <v>28</v>
@@ -10159,7 +10159,7 @@
         <v>32</v>
       </c>
       <c r="AJ50" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK50" t="n">
         <v>44</v>
@@ -10216,7 +10216,7 @@
         <v>5.1</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD50" t="n">
         <v>4.9</v>
@@ -10228,11 +10228,11 @@
         <v>21</v>
       </c>
       <c r="BG50" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
         <v>1.6</v>
       </c>
       <c r="S51" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="T51" t="n">
         <v>1.52</v>
@@ -10311,10 +10311,10 @@
         <v>2.52</v>
       </c>
       <c r="V51" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W51" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X51" t="n">
         <v>1000</v>
@@ -10335,7 +10335,7 @@
         <v>12</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE51" t="n">
         <v>1000</v>
@@ -10371,7 +10371,7 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AQ51" t="n">
         <v>3.4</v>
@@ -10380,7 +10380,7 @@
         <v>3.55</v>
       </c>
       <c r="AS51" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AT51" t="n">
         <v>3.55</v>
@@ -10392,16 +10392,16 @@
         <v>3.25</v>
       </c>
       <c r="AW51" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AX51" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AY51" t="n">
         <v>3.4</v>
       </c>
       <c r="AZ51" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BA51" t="n">
         <v>3.75</v>
@@ -10413,20 +10413,20 @@
         <v>3.8</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE51" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF51" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="BG51" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -10457,19 +10457,19 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G52" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H52" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I52" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="J52" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
         <v>4.6</v>
@@ -10481,34 +10481,34 @@
         <v>1.02</v>
       </c>
       <c r="N52" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
         <v>1.16</v>
       </c>
       <c r="P52" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="Q52" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W52" t="n">
         <v>1.41</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U52" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.37</v>
       </c>
       <c r="X52" t="n">
         <v>36</v>
@@ -10523,7 +10523,7 @@
         <v>34</v>
       </c>
       <c r="AB52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC52" t="n">
         <v>13</v>
@@ -10535,7 +10535,7 @@
         <v>24</v>
       </c>
       <c r="AF52" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG52" t="n">
         <v>18</v>
@@ -10556,7 +10556,7 @@
         <v>40</v>
       </c>
       <c r="AM52" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN52" t="n">
         <v>22</v>
@@ -10574,7 +10574,7 @@
         <v>16</v>
       </c>
       <c r="AS52" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AT52" t="n">
         <v>18</v>
@@ -10583,7 +10583,7 @@
         <v>9.4</v>
       </c>
       <c r="AV52" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW52" t="n">
         <v>17</v>
@@ -10601,16 +10601,16 @@
         <v>3.75</v>
       </c>
       <c r="BB52" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC52" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BD52" t="n">
         <v>3.85</v>
       </c>
       <c r="BE52" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF52" t="n">
         <v>13</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -10684,13 +10684,13 @@
         <v>2.82</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R53" t="n">
         <v>1.74</v>
       </c>
       <c r="S53" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="T53" t="n">
         <v>1.47</v>
@@ -10702,19 +10702,19 @@
         <v>1.33</v>
       </c>
       <c r="W53" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X53" t="n">
         <v>38</v>
       </c>
       <c r="Y53" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z53" t="n">
         <v>40</v>
       </c>
       <c r="AA53" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB53" t="n">
         <v>19</v>
@@ -10750,7 +10750,7 @@
         <v>28</v>
       </c>
       <c r="AM53" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN53" t="n">
         <v>8.6</v>
@@ -10759,13 +10759,13 @@
         <v>25</v>
       </c>
       <c r="AP53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ53" t="n">
         <v>20</v>
       </c>
       <c r="AR53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS53" t="n">
         <v>4.8</v>
@@ -10792,7 +10792,7 @@
         <v>12.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB53" t="n">
         <v>19.5</v>
@@ -10804,7 +10804,7 @@
         <v>20</v>
       </c>
       <c r="BE53" t="n">
-        <v>4.7</v>
+        <v>40</v>
       </c>
       <c r="BF53" t="n">
         <v>5.8</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -10848,13 +10848,13 @@
         <v>2.26</v>
       </c>
       <c r="G54" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H54" t="n">
         <v>2.9</v>
       </c>
       <c r="I54" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>4</v>
@@ -10893,10 +10893,10 @@
         <v>2.82</v>
       </c>
       <c r="V54" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W54" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X54" t="n">
         <v>34</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -11111,7 +11111,7 @@
         <v>970</v>
       </c>
       <c r="AD55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE55" t="n">
         <v>60</v>
@@ -11147,19 +11147,19 @@
         <v>50</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AR55" t="n">
         <v>2.38</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AT55" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU55" t="n">
         <v>4.9</v>
@@ -11168,31 +11168,31 @@
         <v>3</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AX55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY55" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BA55" t="n">
         <v>2.4</v>
       </c>
       <c r="BB55" t="n">
-        <v>2.98</v>
+        <v>5.9</v>
       </c>
       <c r="BC55" t="n">
         <v>5.6</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BE55" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BF55" t="n">
         <v>4.1</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -11236,16 +11236,16 @@
         <v>5.1</v>
       </c>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H56" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="I56" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K56" t="n">
         <v>980</v>
@@ -11272,19 +11272,19 @@
         <v>1.69</v>
       </c>
       <c r="S56" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="T56" t="n">
         <v>1.46</v>
       </c>
       <c r="U56" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V56" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="W56" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11296,7 +11296,7 @@
         <v>18.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB56" t="n">
         <v>980</v>
@@ -11308,7 +11308,7 @@
         <v>15.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF56" t="n">
         <v>70</v>
@@ -11338,65 +11338,65 @@
         <v>1000</v>
       </c>
       <c r="AO56" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR56" t="n">
         <v>2.28</v>
       </c>
-      <c r="AR56" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AS56" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AW56" t="n">
         <v>2.32</v>
       </c>
-      <c r="AT56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AX56" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AY56" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AZ56" t="n">
         <v>2.38</v>
       </c>
-      <c r="AZ56" t="n">
-        <v>2.34</v>
-      </c>
       <c r="BA56" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BB56" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BD56" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BE56" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BF56" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BG56" t="n">
         <v>3.85</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -11433,10 +11433,10 @@
         <v>2.02</v>
       </c>
       <c r="H57" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J57" t="n">
         <v>3.95</v>
@@ -11457,10 +11457,10 @@
         <v>1.19</v>
       </c>
       <c r="P57" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="R57" t="n">
         <v>1.44</v>
@@ -11469,13 +11469,13 @@
         <v>2.48</v>
       </c>
       <c r="T57" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U57" t="n">
         <v>1.11</v>
       </c>
       <c r="V57" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W57" t="n">
         <v>1.98</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -11621,13 +11621,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G58" t="n">
         <v>2.58</v>
       </c>
       <c r="H58" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I58" t="n">
         <v>2.92</v>
@@ -11684,7 +11684,7 @@
         <v>24</v>
       </c>
       <c r="AA58" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB58" t="n">
         <v>18</v>
@@ -11729,7 +11729,7 @@
         <v>14</v>
       </c>
       <c r="AP58" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ58" t="n">
         <v>16.5</v>
@@ -11762,19 +11762,19 @@
         <v>12.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB58" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC58" t="n">
         <v>20</v>
       </c>
       <c r="BD58" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE58" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF58" t="n">
         <v>9</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -11815,19 +11815,19 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H59" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I59" t="n">
         <v>4.1</v>
       </c>
       <c r="J59" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K59" t="n">
         <v>4</v>
@@ -11851,22 +11851,22 @@
         <v>1.93</v>
       </c>
       <c r="R59" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S59" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T59" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U59" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V59" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W59" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X59" t="n">
         <v>16.5</v>
@@ -11875,7 +11875,7 @@
         <v>970</v>
       </c>
       <c r="Z59" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA59" t="n">
         <v>100</v>
@@ -11956,13 +11956,13 @@
         <v>4</v>
       </c>
       <c r="BA59" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB59" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC59" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="BD59" t="n">
         <v>4.4</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -12039,10 +12039,10 @@
         <v>1.43</v>
       </c>
       <c r="P60" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R60" t="n">
         <v>1.27</v>
@@ -12066,7 +12066,7 @@
         <v>11</v>
       </c>
       <c r="Y60" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z60" t="n">
         <v>29</v>
@@ -12117,7 +12117,7 @@
         <v>80</v>
       </c>
       <c r="AP60" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ60" t="n">
         <v>12</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
         <v>5.3</v>
       </c>
       <c r="I61" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J61" t="n">
         <v>3.65</v>
@@ -12227,7 +12227,7 @@
         <v>1.07</v>
       </c>
       <c r="N61" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O61" t="n">
         <v>1.34</v>
@@ -12242,10 +12242,10 @@
         <v>1.31</v>
       </c>
       <c r="S61" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T61" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U61" t="n">
         <v>1.91</v>
@@ -12257,13 +12257,13 @@
         <v>2.2</v>
       </c>
       <c r="X61" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y61" t="n">
         <v>18.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA61" t="n">
         <v>180</v>
@@ -12281,7 +12281,7 @@
         <v>1000</v>
       </c>
       <c r="AF61" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG61" t="n">
         <v>10.5</v>
@@ -12320,7 +12320,7 @@
         <v>36</v>
       </c>
       <c r="AS61" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT61" t="n">
         <v>7</v>
@@ -12332,19 +12332,19 @@
         <v>18.5</v>
       </c>
       <c r="AW61" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX61" t="n">
         <v>8.6</v>
       </c>
       <c r="AY61" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ61" t="n">
         <v>18.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB61" t="n">
         <v>15.5</v>
@@ -12353,20 +12353,20 @@
         <v>17</v>
       </c>
       <c r="BD61" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE61" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF61" t="n">
         <v>9.6</v>
       </c>
       <c r="BG61" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -12400,13 +12400,13 @@
         <v>3.1</v>
       </c>
       <c r="G62" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H62" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I62" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J62" t="n">
         <v>3.5</v>
@@ -12430,7 +12430,7 @@
         <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="R62" t="n">
         <v>1.13</v>
@@ -12439,16 +12439,16 @@
         <v>2.74</v>
       </c>
       <c r="T62" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U62" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V62" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W62" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
         <v>1.77</v>
       </c>
       <c r="H63" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I63" t="n">
         <v>9.4</v>
@@ -12606,7 +12606,7 @@
         <v>3.85</v>
       </c>
       <c r="K63" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -12785,31 +12785,31 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G64" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H64" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I64" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>3.1</v>
       </c>
       <c r="K64" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L64" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M64" t="n">
         <v>1.09</v>
       </c>
       <c r="N64" t="n">
-        <v>1.68</v>
+        <v>2.64</v>
       </c>
       <c r="O64" t="n">
         <v>1.37</v>
@@ -12830,10 +12830,10 @@
         <v>1.78</v>
       </c>
       <c r="U64" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V64" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W64" t="n">
         <v>1.6</v>
@@ -12845,7 +12845,7 @@
         <v>12.5</v>
       </c>
       <c r="Z64" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA64" t="n">
         <v>75</v>
@@ -12893,40 +12893,40 @@
         <v>1000</v>
       </c>
       <c r="AP64" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AQ64" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR64" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS64" t="n">
-        <v>38</v>
+        <v>3.85</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.92</v>
+        <v>7.8</v>
       </c>
       <c r="AU64" t="n">
-        <v>6.4</v>
+        <v>2.74</v>
       </c>
       <c r="AV64" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AW64" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AX64" t="n">
         <v>12.5</v>
       </c>
       <c r="AY64" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ64" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BA64" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BB64" t="n">
         <v>3.75</v>
@@ -12935,20 +12935,20 @@
         <v>3.7</v>
       </c>
       <c r="BD64" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE64" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF64" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG64" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G65" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="H65" t="n">
         <v>5.8</v>
@@ -13003,34 +13003,34 @@
         <v>1.07</v>
       </c>
       <c r="N65" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O65" t="n">
         <v>1.33</v>
       </c>
       <c r="P65" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q65" t="n">
         <v>1.98</v>
       </c>
       <c r="R65" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S65" t="n">
         <v>3.55</v>
       </c>
       <c r="T65" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="U65" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V65" t="n">
         <v>1.17</v>
       </c>
       <c r="W65" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="X65" t="n">
         <v>14.5</v>
@@ -13048,7 +13048,7 @@
         <v>8</v>
       </c>
       <c r="AC65" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD65" t="n">
         <v>25</v>
@@ -13069,7 +13069,7 @@
         <v>110</v>
       </c>
       <c r="AJ65" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK65" t="n">
         <v>19.5</v>
@@ -13093,10 +13093,10 @@
         <v>16</v>
       </c>
       <c r="AR65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS65" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT65" t="n">
         <v>6.8</v>
@@ -13108,7 +13108,7 @@
         <v>20</v>
       </c>
       <c r="AW65" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX65" t="n">
         <v>8.199999999999999</v>
@@ -13120,7 +13120,7 @@
         <v>19.5</v>
       </c>
       <c r="BA65" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB65" t="n">
         <v>14.5</v>
@@ -13129,20 +13129,20 @@
         <v>16</v>
       </c>
       <c r="BD65" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE65" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF65" t="n">
         <v>9.4</v>
       </c>
       <c r="BG65" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G66" t="n">
         <v>5.7</v>
@@ -13197,16 +13197,16 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="O66" t="n">
         <v>1.35</v>
       </c>
       <c r="P66" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="R66" t="n">
         <v>1.24</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -13370,16 +13370,16 @@
         <v>2.32</v>
       </c>
       <c r="G67" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H67" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
         <v>4.1</v>
       </c>
       <c r="J67" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K67" t="n">
         <v>3.15</v>
@@ -13451,7 +13451,7 @@
         <v>11.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI67" t="n">
         <v>75</v>
@@ -13508,7 +13508,7 @@
         <v>19</v>
       </c>
       <c r="BA67" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB67" t="n">
         <v>27</v>
@@ -13523,14 +13523,14 @@
         <v>42</v>
       </c>
       <c r="BF67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG67" t="n">
         <v>60</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -13561,19 +13561,19 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G68" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="J68" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K68" t="n">
         <v>3.5</v>
@@ -13603,16 +13603,16 @@
         <v>3.4</v>
       </c>
       <c r="T68" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U68" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V68" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W68" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="X68" t="n">
         <v>1000</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
         <v>1.64</v>
       </c>
       <c r="G69" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H69" t="n">
         <v>6.2</v>
@@ -13767,10 +13767,10 @@
         <v>7.6</v>
       </c>
       <c r="J69" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K69" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -13785,7 +13785,7 @@
         <v>1.4</v>
       </c>
       <c r="P69" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q69" t="n">
         <v>2.18</v>
@@ -13806,7 +13806,7 @@
         <v>1.15</v>
       </c>
       <c r="W69" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X69" t="n">
         <v>14</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -13952,19 +13952,19 @@
         <v>1.99</v>
       </c>
       <c r="G70" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H70" t="n">
         <v>3.95</v>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K70" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
@@ -13973,19 +13973,19 @@
         <v>1.05</v>
       </c>
       <c r="N70" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="O70" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P70" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
         <v>1.87</v>
       </c>
       <c r="R70" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S70" t="n">
         <v>2.84</v>
@@ -13994,13 +13994,13 @@
         <v>1.54</v>
       </c>
       <c r="U70" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V70" t="n">
         <v>1.3</v>
       </c>
       <c r="W70" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X70" t="n">
         <v>20</v>
@@ -14042,10 +14042,10 @@
         <v>32</v>
       </c>
       <c r="AK70" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL70" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM70" t="n">
         <v>1000</v>
@@ -14057,7 +14057,7 @@
         <v>1000</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AQ70" t="n">
         <v>2.26</v>
@@ -14066,7 +14066,7 @@
         <v>2.4</v>
       </c>
       <c r="AS70" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AT70" t="n">
         <v>2.12</v>
@@ -14078,41 +14078,41 @@
         <v>2.28</v>
       </c>
       <c r="AW70" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AX70" t="n">
         <v>2.22</v>
       </c>
       <c r="AY70" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AZ70" t="n">
         <v>2.3</v>
       </c>
       <c r="BA70" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BB70" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BC70" t="n">
         <v>2.34</v>
       </c>
       <c r="BD70" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BE70" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BF70" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BG70" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -14149,16 +14149,16 @@
         <v>3.5</v>
       </c>
       <c r="H71" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I71" t="n">
         <v>2.5</v>
       </c>
       <c r="J71" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K71" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14182,10 +14182,10 @@
         <v>1.4</v>
       </c>
       <c r="S71" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T71" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U71" t="n">
         <v>2.22</v>
@@ -14269,10 +14269,10 @@
         <v>4.1</v>
       </c>
       <c r="AV71" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AW71" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AX71" t="n">
         <v>1.86</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H72" t="n">
         <v>3.05</v>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -14361,13 +14361,13 @@
         <v>1.01</v>
       </c>
       <c r="N72" t="n">
-        <v>1.63</v>
+        <v>2.68</v>
       </c>
       <c r="O72" t="n">
         <v>1.37</v>
       </c>
       <c r="P72" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q72" t="n">
         <v>1.92</v>
@@ -14379,16 +14379,16 @@
         <v>3.2</v>
       </c>
       <c r="T72" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U72" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V72" t="n">
         <v>1.41</v>
       </c>
       <c r="W72" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -14531,22 +14531,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G73" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H73" t="n">
         <v>2.82</v>
       </c>
       <c r="I73" t="n">
-        <v>970</v>
+        <v>4.5</v>
       </c>
       <c r="J73" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14555,13 +14555,13 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.76</v>
+        <v>2.66</v>
       </c>
       <c r="O73" t="n">
         <v>1.29</v>
       </c>
       <c r="P73" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q73" t="n">
         <v>1.76</v>
@@ -14573,16 +14573,16 @@
         <v>2.84</v>
       </c>
       <c r="T73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V73" t="n">
         <v>1.45</v>
       </c>
       <c r="W73" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X73" t="n">
         <v>1000</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G74" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H74" t="n">
         <v>2.68</v>
@@ -14737,10 +14737,10 @@
         <v>3.1</v>
       </c>
       <c r="J74" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K74" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L74" t="n">
         <v>1.01</v>
@@ -14755,28 +14755,28 @@
         <v>1.32</v>
       </c>
       <c r="P74" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R74" t="n">
         <v>1.31</v>
       </c>
       <c r="S74" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T74" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="U74" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="V74" t="n">
         <v>1.47</v>
       </c>
       <c r="W74" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X74" t="n">
         <v>970</v>
@@ -14785,7 +14785,7 @@
         <v>970</v>
       </c>
       <c r="Z74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA74" t="n">
         <v>55</v>
@@ -14827,7 +14827,7 @@
         <v>120</v>
       </c>
       <c r="AN74" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO74" t="n">
         <v>38</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -14919,170 +14919,170 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="G75" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="H75" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P75" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X75" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF75" t="n">
         <v>8.6</v>
       </c>
-      <c r="I75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J75" t="n">
-        <v>5</v>
-      </c>
-      <c r="K75" t="n">
-        <v>14</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P75" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R75" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S75" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W75" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG75" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH75" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI75" t="n">
         <v>1000</v>
       </c>
       <c r="AJ75" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK75" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL75" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM75" t="n">
         <v>1000</v>
       </c>
       <c r="AN75" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO75" t="n">
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU75" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV75" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW75" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX75" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY75" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ75" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA75" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC75" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD75" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE75" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF75" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG75" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -15113,22 +15113,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G76" t="n">
         <v>1.52</v>
       </c>
       <c r="H76" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J76" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K76" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L76" t="n">
         <v>1.34</v>
@@ -15137,10 +15137,10 @@
         <v>1.05</v>
       </c>
       <c r="N76" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O76" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P76" t="n">
         <v>2.22</v>
@@ -15149,115 +15149,115 @@
         <v>1.76</v>
       </c>
       <c r="R76" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S76" t="n">
         <v>2.92</v>
       </c>
       <c r="T76" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U76" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V76" t="n">
         <v>1.14</v>
       </c>
       <c r="W76" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="X76" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y76" t="n">
         <v>26</v>
       </c>
       <c r="Z76" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA76" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB76" t="n">
         <v>9</v>
       </c>
       <c r="AC76" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD76" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE76" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF76" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG76" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH76" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI76" t="n">
         <v>95</v>
       </c>
       <c r="AJ76" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK76" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL76" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM76" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN76" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO76" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AP76" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ76" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR76" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="AS76" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="AT76" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU76" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW76" t="n">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AX76" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY76" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA76" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BB76" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC76" t="n">
         <v>14</v>
@@ -15266,17 +15266,17 @@
         <v>28</v>
       </c>
       <c r="BE76" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BF76" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG76" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -15307,73 +15307,73 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G77" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H77" t="n">
         <v>1.63</v>
       </c>
       <c r="I77" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="J77" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K77" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L77" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M77" t="n">
         <v>1.07</v>
       </c>
       <c r="N77" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O77" t="n">
         <v>1.31</v>
       </c>
       <c r="P77" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R77" t="n">
         <v>1.33</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T77" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U77" t="n">
         <v>1.89</v>
       </c>
       <c r="V77" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W77" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X77" t="n">
         <v>18</v>
       </c>
       <c r="Y77" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z77" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA77" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC77" t="n">
         <v>11</v>
@@ -15388,25 +15388,25 @@
         <v>60</v>
       </c>
       <c r="AG77" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH77" t="n">
         <v>27</v>
       </c>
       <c r="AI77" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ77" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AK77" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL77" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM77" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN77" t="n">
         <v>1000</v>
@@ -15421,28 +15421,28 @@
         <v>7</v>
       </c>
       <c r="AR77" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS77" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT77" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU77" t="n">
         <v>7.8</v>
       </c>
       <c r="AV77" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW77" t="n">
         <v>15.5</v>
       </c>
       <c r="AX77" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ77" t="n">
         <v>18.5</v>
@@ -15460,7 +15460,7 @@
         <v>4.2</v>
       </c>
       <c r="BE77" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF77" t="n">
         <v>4.2</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -15501,19 +15501,19 @@
         </is>
       </c>
       <c r="F78" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G78" t="n">
         <v>3.55</v>
       </c>
-      <c r="G78" t="n">
-        <v>3.65</v>
-      </c>
       <c r="H78" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I78" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K78" t="n">
         <v>3.65</v>
@@ -15537,22 +15537,22 @@
         <v>2.1</v>
       </c>
       <c r="R78" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S78" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T78" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U78" t="n">
         <v>2.08</v>
       </c>
       <c r="V78" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W78" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X78" t="n">
         <v>13</v>
@@ -15579,13 +15579,13 @@
         <v>25</v>
       </c>
       <c r="AF78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG78" t="n">
         <v>15</v>
       </c>
       <c r="AH78" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI78" t="n">
         <v>42</v>
@@ -15606,13 +15606,13 @@
         <v>48</v>
       </c>
       <c r="AO78" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP78" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ78" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR78" t="n">
         <v>12.5</v>
@@ -15627,7 +15627,7 @@
         <v>7.2</v>
       </c>
       <c r="AV78" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW78" t="n">
         <v>22</v>
@@ -15639,16 +15639,16 @@
         <v>13.5</v>
       </c>
       <c r="AZ78" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA78" t="n">
         <v>36</v>
       </c>
       <c r="BB78" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BC78" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD78" t="n">
         <v>50</v>
@@ -15657,14 +15657,14 @@
         <v>40</v>
       </c>
       <c r="BF78" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BG78" t="n">
         <v>17.5</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15710,7 @@
         <v>2.72</v>
       </c>
       <c r="K79" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L79" t="n">
         <v>1.4</v>
@@ -15719,7 +15719,7 @@
         <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="O79" t="n">
         <v>1.02</v>
@@ -15734,13 +15734,13 @@
         <v>1.18</v>
       </c>
       <c r="S79" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="T79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V79" t="n">
         <v>1.25</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
         <v>1.65</v>
       </c>
       <c r="G80" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="H80" t="n">
         <v>1.09</v>
@@ -15901,37 +15901,37 @@
         <v>8</v>
       </c>
       <c r="J80" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K80" t="n">
         <v>3.85</v>
       </c>
       <c r="L80" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M80" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N80" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="O80" t="n">
         <v>1.53</v>
       </c>
       <c r="P80" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q80" t="n">
         <v>2.58</v>
       </c>
       <c r="R80" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S80" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T80" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U80" t="n">
         <v>1.56</v>
@@ -15940,13 +15940,13 @@
         <v>1.14</v>
       </c>
       <c r="W80" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="X80" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y80" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z80" t="n">
         <v>65</v>
@@ -15955,10 +15955,10 @@
         <v>1000</v>
       </c>
       <c r="AB80" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AC80" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD80" t="n">
         <v>34</v>
@@ -15967,7 +15967,7 @@
         <v>1000</v>
       </c>
       <c r="AF80" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG80" t="n">
         <v>12</v>
@@ -15979,10 +15979,10 @@
         <v>1000</v>
       </c>
       <c r="AJ80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK80" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL80" t="n">
         <v>75</v>
@@ -15997,62 +15997,62 @@
         <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR80" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS80" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AU80" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV80" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW80" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX80" t="n">
         <v>4.2</v>
       </c>
       <c r="AY80" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ80" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA80" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB80" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF80" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC80" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD80" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE80" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF80" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG80" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -16083,19 +16083,19 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G81" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H81" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="I81" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J81" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="K81" t="n">
         <v>4.2</v>
@@ -16113,7 +16113,7 @@
         <v>1.58</v>
       </c>
       <c r="P81" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q81" t="n">
         <v>2.88</v>
@@ -16125,16 +16125,16 @@
         <v>2.88</v>
       </c>
       <c r="T81" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U81" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V81" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W81" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X81" t="n">
         <v>1000</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -16277,25 +16277,25 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G82" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H82" t="n">
-        <v>8</v>
+        <v>1.09</v>
       </c>
       <c r="I82" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="J82" t="n">
         <v>3.5</v>
       </c>
       <c r="K82" t="n">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="L82" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M82" t="n">
         <v>1.01</v>
@@ -16304,19 +16304,19 @@
         <v>1.48</v>
       </c>
       <c r="O82" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P82" t="n">
         <v>1.48</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R82" t="n">
         <v>1.12</v>
       </c>
       <c r="S82" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T82" t="n">
         <v>1.01</v>
@@ -16325,7 +16325,7 @@
         <v>1.01</v>
       </c>
       <c r="V82" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W82" t="n">
         <v>2.56</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -16471,46 +16471,46 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="G83" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H83" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I83" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J83" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="K83" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L83" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M83" t="n">
         <v>1.01</v>
       </c>
       <c r="N83" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O83" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="P83" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R83" t="n">
         <v>1.12</v>
       </c>
       <c r="S83" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T83" t="n">
         <v>1.01</v>
@@ -16522,7 +16522,7 @@
         <v>1.14</v>
       </c>
       <c r="W83" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="X83" t="n">
         <v>1000</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -16680,22 +16680,22 @@
         <v>3.1</v>
       </c>
       <c r="K84" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L84" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M84" t="n">
         <v>1.13</v>
       </c>
       <c r="N84" t="n">
-        <v>1.47</v>
+        <v>2.44</v>
       </c>
       <c r="O84" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="P84" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q84" t="n">
         <v>2.78</v>
@@ -16707,10 +16707,10 @@
         <v>5</v>
       </c>
       <c r="T84" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="U84" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="V84" t="n">
         <v>1.24</v>
@@ -16719,116 +16719,116 @@
         <v>1.83</v>
       </c>
       <c r="X84" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y84" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z84" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA84" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB84" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC84" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC84" t="n">
-        <v>9</v>
-      </c>
       <c r="AD84" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE84" t="n">
         <v>1000</v>
       </c>
       <c r="AF84" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG84" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH84" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI84" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ84" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK84" t="n">
         <v>34</v>
       </c>
-      <c r="AK84" t="n">
-        <v>36</v>
-      </c>
       <c r="AL84" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM84" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN84" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO84" t="n">
         <v>1000</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="AQ84" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR84" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="AS84" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.95</v>
+        <v>5.6</v>
       </c>
       <c r="AU84" t="n">
-        <v>2.02</v>
+        <v>6.4</v>
       </c>
       <c r="AV84" t="n">
-        <v>2.36</v>
+        <v>18</v>
       </c>
       <c r="AW84" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX84" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="AY84" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="AZ84" t="n">
-        <v>2.4</v>
+        <v>23</v>
       </c>
       <c r="BA84" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB84" t="n">
-        <v>2.42</v>
+        <v>21</v>
       </c>
       <c r="BC84" t="n">
-        <v>2.42</v>
+        <v>24</v>
       </c>
       <c r="BD84" t="n">
-        <v>46</v>
+        <v>7.2</v>
       </c>
       <c r="BE84" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF84" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG84" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -16871,10 +16871,10 @@
         <v>4.5</v>
       </c>
       <c r="J85" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K85" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L85" t="n">
         <v>1.01</v>
@@ -16883,7 +16883,7 @@
         <v>1.08</v>
       </c>
       <c r="N85" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O85" t="n">
         <v>1.37</v>
@@ -16895,7 +16895,7 @@
         <v>2.1</v>
       </c>
       <c r="R85" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S85" t="n">
         <v>3.85</v>
@@ -16910,7 +16910,7 @@
         <v>1.29</v>
       </c>
       <c r="W85" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X85" t="n">
         <v>14</v>
@@ -16937,7 +16937,7 @@
         <v>65</v>
       </c>
       <c r="AF85" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG85" t="n">
         <v>12.5</v>
@@ -16961,7 +16961,7 @@
         <v>140</v>
       </c>
       <c r="AN85" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO85" t="n">
         <v>80</v>
@@ -16976,7 +16976,7 @@
         <v>19</v>
       </c>
       <c r="AS85" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT85" t="n">
         <v>7.2</v>
@@ -16988,7 +16988,7 @@
         <v>14</v>
       </c>
       <c r="AW85" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX85" t="n">
         <v>10.5</v>
@@ -17000,7 +17000,7 @@
         <v>16.5</v>
       </c>
       <c r="BA85" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB85" t="n">
         <v>20</v>
@@ -17009,20 +17009,20 @@
         <v>21</v>
       </c>
       <c r="BD85" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE85" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF85" t="n">
         <v>15</v>
       </c>
       <c r="BG85" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -17095,7 +17095,7 @@
         <v>3.5</v>
       </c>
       <c r="T86" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U86" t="n">
         <v>1.76</v>
@@ -17146,13 +17146,13 @@
         <v>970</v>
       </c>
       <c r="AK86" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL86" t="n">
         <v>55</v>
       </c>
       <c r="AM86" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN86" t="n">
         <v>9.800000000000001</v>
@@ -17161,16 +17161,16 @@
         <v>310</v>
       </c>
       <c r="AP86" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ86" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR86" t="n">
         <v>8</v>
       </c>
       <c r="AS86" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT86" t="n">
         <v>6</v>
@@ -17179,10 +17179,10 @@
         <v>4.8</v>
       </c>
       <c r="AV86" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW86" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX86" t="n">
         <v>7.2</v>
@@ -17203,10 +17203,10 @@
         <v>6</v>
       </c>
       <c r="BD86" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE86" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF86" t="n">
         <v>7.8</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
         <v>5.6</v>
       </c>
       <c r="J87" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K87" t="n">
         <v>3.7</v>
@@ -17271,28 +17271,28 @@
         <v>1.1</v>
       </c>
       <c r="N87" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O87" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P87" t="n">
         <v>1.6</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="R87" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S87" t="n">
         <v>4</v>
       </c>
       <c r="T87" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U87" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="V87" t="n">
         <v>1.21</v>
@@ -17310,7 +17310,7 @@
         <v>40</v>
       </c>
       <c r="AA87" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB87" t="n">
         <v>7.2</v>
@@ -17322,7 +17322,7 @@
         <v>22</v>
       </c>
       <c r="AE87" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF87" t="n">
         <v>11.5</v>
@@ -17343,74 +17343,74 @@
         <v>26</v>
       </c>
       <c r="AL87" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM87" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN87" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO87" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP87" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX87" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ87" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR87" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS87" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT87" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU87" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV87" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW87" t="n">
+      <c r="AY87" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD87" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX87" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY87" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ87" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA87" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB87" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC87" t="n">
+      <c r="BE87" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF87" t="n">
         <v>5.8</v>
       </c>
-      <c r="BD87" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE87" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF87" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG87" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
         <v>4.5</v>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J88" t="n">
         <v>3.5</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -17635,22 +17635,22 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G89" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H89" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I89" t="n">
         <v>3.65</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K89" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L89" t="n">
         <v>1.31</v>
@@ -17680,13 +17680,13 @@
         <v>1.72</v>
       </c>
       <c r="U89" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V89" t="n">
         <v>1.37</v>
       </c>
       <c r="W89" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X89" t="n">
         <v>15</v>
@@ -17707,7 +17707,7 @@
         <v>8.4</v>
       </c>
       <c r="AD89" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE89" t="n">
         <v>42</v>
@@ -17725,10 +17725,10 @@
         <v>55</v>
       </c>
       <c r="AJ89" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK89" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL89" t="n">
         <v>42</v>
@@ -17737,68 +17737,68 @@
         <v>110</v>
       </c>
       <c r="AN89" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO89" t="n">
         <v>40</v>
       </c>
       <c r="AP89" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ89" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ89" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR89" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS89" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT89" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU89" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV89" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW89" t="n">
+      <c r="BA89" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE89" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX89" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY89" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ89" t="n">
+      <c r="BF89" t="n">
         <v>5.6</v>
       </c>
-      <c r="BA89" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB89" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC89" t="n">
+      <c r="BG89" t="n">
         <v>6.2</v>
       </c>
-      <c r="BD89" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE89" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF89" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG89" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -17832,13 +17832,13 @@
         <v>1.62</v>
       </c>
       <c r="G90" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H90" t="n">
         <v>6.6</v>
       </c>
       <c r="I90" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J90" t="n">
         <v>3.45</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -18023,58 +18023,58 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G91" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H91" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I91" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J91" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K91" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L91" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M91" t="n">
         <v>1.07</v>
       </c>
       <c r="N91" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O91" t="n">
         <v>1.31</v>
       </c>
       <c r="P91" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q91" t="n">
         <v>1.88</v>
       </c>
       <c r="R91" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S91" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T91" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U91" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V91" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W91" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X91" t="n">
         <v>970</v>
@@ -18083,10 +18083,10 @@
         <v>970</v>
       </c>
       <c r="Z91" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA91" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AB91" t="n">
         <v>970</v>
@@ -18095,10 +18095,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD91" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE91" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF91" t="n">
         <v>970</v>
@@ -18107,16 +18107,16 @@
         <v>970</v>
       </c>
       <c r="AH91" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI91" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ91" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK91" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL91" t="n">
         <v>38</v>
@@ -18131,62 +18131,62 @@
         <v>46</v>
       </c>
       <c r="AP91" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AQ91" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AR91" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS91" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AT91" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU91" t="n">
         <v>7.2</v>
       </c>
       <c r="AV91" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AW91" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX91" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY91" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ91" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC91" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA91" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB91" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC91" t="n">
+      <c r="BD91" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG91" t="n">
         <v>8.4</v>
       </c>
-      <c r="BD91" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE91" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF91" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG91" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -18223,16 +18223,16 @@
         <v>1.41</v>
       </c>
       <c r="H92" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I92" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J92" t="n">
         <v>4.9</v>
       </c>
       <c r="K92" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -18241,34 +18241,34 @@
         <v>1.06</v>
       </c>
       <c r="N92" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O92" t="n">
         <v>1.3</v>
       </c>
       <c r="P92" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q92" t="n">
         <v>1.88</v>
       </c>
       <c r="R92" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S92" t="n">
         <v>3.25</v>
       </c>
       <c r="T92" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U92" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V92" t="n">
         <v>1.07</v>
       </c>
       <c r="W92" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="X92" t="n">
         <v>18</v>
@@ -18277,22 +18277,22 @@
         <v>34</v>
       </c>
       <c r="Z92" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA92" t="n">
         <v>1000</v>
       </c>
       <c r="AB92" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC92" t="n">
         <v>12.5</v>
       </c>
       <c r="AD92" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AE92" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AF92" t="n">
         <v>7.4</v>
@@ -18304,7 +18304,7 @@
         <v>38</v>
       </c>
       <c r="AI92" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AJ92" t="n">
         <v>11</v>
@@ -18313,10 +18313,10 @@
         <v>17.5</v>
       </c>
       <c r="AL92" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM92" t="n">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AN92" t="n">
         <v>7.2</v>
@@ -18325,19 +18325,19 @@
         <v>1000</v>
       </c>
       <c r="AP92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ92" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR92" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS92" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT92" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU92" t="n">
         <v>10</v>
@@ -18346,7 +18346,7 @@
         <v>7.8</v>
       </c>
       <c r="AW92" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX92" t="n">
         <v>6</v>
@@ -18358,29 +18358,29 @@
         <v>7.4</v>
       </c>
       <c r="BA92" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB92" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC92" t="n">
         <v>14</v>
       </c>
       <c r="BD92" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE92" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF92" t="n">
         <v>5.9</v>
       </c>
       <c r="BG92" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
@@ -18411,19 +18411,19 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G93" t="n">
         <v>2.28</v>
       </c>
       <c r="H93" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I93" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J93" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K93" t="n">
         <v>4</v>
@@ -18441,25 +18441,25 @@
         <v>1.26</v>
       </c>
       <c r="P93" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q93" t="n">
         <v>1.75</v>
       </c>
       <c r="R93" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S93" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T93" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U93" t="n">
         <v>2.38</v>
       </c>
       <c r="V93" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W93" t="n">
         <v>1.78</v>
@@ -18510,7 +18510,7 @@
         <v>34</v>
       </c>
       <c r="AM93" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN93" t="n">
         <v>14</v>
@@ -18546,13 +18546,13 @@
         <v>13</v>
       </c>
       <c r="AY93" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ93" t="n">
         <v>14</v>
       </c>
       <c r="BA93" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB93" t="n">
         <v>24</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-12 04:53:44</t>
+          <t>2026-03-12 07:12:09</t>
         </is>
       </c>
     </row>
